--- a/research/traditional_assets/database/data/hong_kong/hong_kong_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_oilfield_svcs_equip.xlsx
@@ -1775,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1912,22 +1912,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08680728045993849</v>
+        <v>0.08670162344717959</v>
       </c>
       <c r="C2">
-        <v>4.542279218529581</v>
+        <v>4.499805640960903</v>
       </c>
       <c r="D2">
-        <v>2.422279218529581</v>
+        <v>2.425105640960903</v>
       </c>
       <c r="E2">
-        <v>-3.200000000000001</v>
+        <v>-3.154700000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.04530000000000001</v>
       </c>
       <c r="G2">
         <v>2.12</v>
@@ -1948,28 +1948,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00227859</v>
       </c>
       <c r="N2">
-        <v>0.6046666666666667</v>
+        <v>0.6023880766666667</v>
       </c>
       <c r="O2">
-        <v>0.09977000000000001</v>
+        <v>0.09939403265000002</v>
       </c>
       <c r="P2">
-        <v>0.5048966666666667</v>
+        <v>0.5029940440166667</v>
       </c>
       <c r="Q2">
-        <v>0.7518966666666667</v>
+        <v>0.7499940440166667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08680728045993849</v>
+        <v>0.08715314994664605</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751832</v>
+        <v>0.8060498630376507</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>265.3687880077884</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1994,22 +1994,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08670162344717959</v>
+        <v>0.08659596643442068</v>
       </c>
       <c r="C3">
-        <v>4.499805640960903</v>
+        <v>4.457338667086889</v>
       </c>
       <c r="D3">
-        <v>2.425105640960903</v>
+        <v>2.427938667086889</v>
       </c>
       <c r="E3">
-        <v>-3.154700000000001</v>
+        <v>-3.1094</v>
       </c>
       <c r="F3">
-        <v>0.04530000000000001</v>
+        <v>0.09060000000000003</v>
       </c>
       <c r="G3">
         <v>2.12</v>
@@ -2030,28 +2030,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M3">
-        <v>0.00227859</v>
+        <v>0.004557180000000001</v>
       </c>
       <c r="N3">
-        <v>0.6023880766666667</v>
+        <v>0.6001094866666666</v>
       </c>
       <c r="O3">
-        <v>0.09939403265000002</v>
+        <v>0.0990180653</v>
       </c>
       <c r="P3">
-        <v>0.5029940440166667</v>
+        <v>0.5010914213666666</v>
       </c>
       <c r="Q3">
-        <v>0.7499940440166667</v>
+        <v>0.7480914213666666</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08715314994664605</v>
+        <v>0.08750607799430682</v>
       </c>
       <c r="T3">
-        <v>0.8060498630376507</v>
+        <v>0.8129290875911889</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>265.3687880077884</v>
+        <v>132.6843940038942</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2076,22 +2076,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08659596643442068</v>
+        <v>0.08649030942166179</v>
       </c>
       <c r="C4">
-        <v>4.457338667086889</v>
+        <v>4.414878320078059</v>
       </c>
       <c r="D4">
-        <v>2.427938667086889</v>
+        <v>2.43077832007806</v>
       </c>
       <c r="E4">
-        <v>-3.1094</v>
+        <v>-3.064100000000001</v>
       </c>
       <c r="F4">
-        <v>0.09060000000000003</v>
+        <v>0.1359</v>
       </c>
       <c r="G4">
         <v>2.12</v>
@@ -2112,28 +2112,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M4">
-        <v>0.004557180000000001</v>
+        <v>0.006835770000000001</v>
       </c>
       <c r="N4">
-        <v>0.6001094866666666</v>
+        <v>0.5978308966666667</v>
       </c>
       <c r="O4">
-        <v>0.0990180653</v>
+        <v>0.09864209795000001</v>
       </c>
       <c r="P4">
-        <v>0.5010914213666666</v>
+        <v>0.4991887987166667</v>
       </c>
       <c r="Q4">
-        <v>0.7480914213666666</v>
+        <v>0.7461887987166667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08750607799430682</v>
+        <v>0.08786628290892969</v>
       </c>
       <c r="T4">
-        <v>0.8129290875911889</v>
+        <v>0.8199501518262434</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>132.6843940038942</v>
+        <v>88.45626266926281</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2158,22 +2158,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08649030942166179</v>
+        <v>0.08638465240890289</v>
       </c>
       <c r="C5">
-        <v>4.414878320078059</v>
+        <v>4.372424623213463</v>
       </c>
       <c r="D5">
-        <v>2.43077832007806</v>
+        <v>2.433624623213463</v>
       </c>
       <c r="E5">
-        <v>-3.064100000000001</v>
+        <v>-3.018800000000001</v>
       </c>
       <c r="F5">
-        <v>0.1359</v>
+        <v>0.1812000000000001</v>
       </c>
       <c r="G5">
         <v>2.12</v>
@@ -2194,28 +2194,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M5">
-        <v>0.006835770000000001</v>
+        <v>0.009114360000000002</v>
       </c>
       <c r="N5">
-        <v>0.5978308966666667</v>
+        <v>0.5955523066666667</v>
       </c>
       <c r="O5">
-        <v>0.09864209795000001</v>
+        <v>0.09826613060000002</v>
       </c>
       <c r="P5">
-        <v>0.4991887987166667</v>
+        <v>0.4972861760666667</v>
       </c>
       <c r="Q5">
-        <v>0.7461887987166667</v>
+        <v>0.7442861760666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08786628290892969</v>
+        <v>0.08823399209260718</v>
       </c>
       <c r="T5">
-        <v>0.8199501518262434</v>
+        <v>0.8271174882328616</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>88.45626266926281</v>
+        <v>66.3421970019471</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2240,22 +2240,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08638465240890289</v>
+        <v>0.08627899539614399</v>
       </c>
       <c r="C6">
-        <v>4.372424623213463</v>
+        <v>4.329977599881307</v>
       </c>
       <c r="D6">
-        <v>2.433624623213463</v>
+        <v>2.436477599881306</v>
       </c>
       <c r="E6">
-        <v>-3.018800000000001</v>
+        <v>-2.9735</v>
       </c>
       <c r="F6">
-        <v>0.1812000000000001</v>
+        <v>0.2265000000000001</v>
       </c>
       <c r="G6">
         <v>2.12</v>
@@ -2276,28 +2276,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M6">
-        <v>0.009114360000000002</v>
+        <v>0.01139295</v>
       </c>
       <c r="N6">
-        <v>0.5955523066666667</v>
+        <v>0.5932737166666667</v>
       </c>
       <c r="O6">
-        <v>0.09826613060000002</v>
+        <v>0.09789016325000001</v>
       </c>
       <c r="P6">
-        <v>0.4972861760666667</v>
+        <v>0.4953835534166667</v>
       </c>
       <c r="Q6">
-        <v>0.7442861760666667</v>
+        <v>0.7423835534166667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08823399209260718</v>
+        <v>0.08860944252225683</v>
       </c>
       <c r="T6">
-        <v>0.8271174882328616</v>
+        <v>0.8344357159322505</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>66.3421970019471</v>
+        <v>53.07375760155768</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2322,22 +2322,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08627899539614399</v>
+        <v>0.0861733383833851</v>
       </c>
       <c r="C7">
-        <v>4.329977599881307</v>
+        <v>4.287537273579599</v>
       </c>
       <c r="D7">
-        <v>2.436477599881306</v>
+        <v>2.4393372735796</v>
       </c>
       <c r="E7">
-        <v>-2.9735</v>
+        <v>-2.9282</v>
       </c>
       <c r="F7">
-        <v>0.2265000000000001</v>
+        <v>0.2718000000000001</v>
       </c>
       <c r="G7">
         <v>2.12</v>
@@ -2358,28 +2358,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M7">
-        <v>0.01139295</v>
+        <v>0.01367154</v>
       </c>
       <c r="N7">
-        <v>0.5932737166666667</v>
+        <v>0.5909951266666666</v>
       </c>
       <c r="O7">
-        <v>0.09789016325000001</v>
+        <v>0.0975141959</v>
       </c>
       <c r="P7">
-        <v>0.4953835534166667</v>
+        <v>0.4934809307666667</v>
       </c>
       <c r="Q7">
-        <v>0.7423835534166667</v>
+        <v>0.7404809307666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08860944252225683</v>
+        <v>0.08899288125892033</v>
       </c>
       <c r="T7">
-        <v>0.8344357159322505</v>
+        <v>0.8419096506039669</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>53.07375760155768</v>
+        <v>44.22813133463139</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2404,22 +2404,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08617333838338509</v>
+        <v>0.0860676813706262</v>
       </c>
       <c r="C8">
-        <v>4.2875372735796</v>
+        <v>4.245103667916801</v>
       </c>
       <c r="D8">
-        <v>2.4393372735796</v>
+        <v>2.442203667916801</v>
       </c>
       <c r="E8">
-        <v>-2.9282</v>
+        <v>-2.882900000000001</v>
       </c>
       <c r="F8">
-        <v>0.2718</v>
+        <v>0.3171</v>
       </c>
       <c r="G8">
         <v>2.12</v>
@@ -2440,28 +2440,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M8">
-        <v>0.01367154</v>
+        <v>0.01595013</v>
       </c>
       <c r="N8">
-        <v>0.5909951266666666</v>
+        <v>0.5887165366666667</v>
       </c>
       <c r="O8">
-        <v>0.0975141959</v>
+        <v>0.09713822855000001</v>
       </c>
       <c r="P8">
-        <v>0.4934809307666667</v>
+        <v>0.4915783081166667</v>
       </c>
       <c r="Q8">
-        <v>0.7404809307666667</v>
+        <v>0.7385783081166667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08899288125892033</v>
+        <v>0.08938456598992064</v>
       </c>
       <c r="T8">
-        <v>0.8419096506039669</v>
+        <v>0.8495443150535696</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>44.2281313346314</v>
+        <v>37.90982685825549</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2486,22 +2486,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08606768137062619</v>
+        <v>0.08596202435786729</v>
       </c>
       <c r="C9">
-        <v>4.245103667916801</v>
+        <v>4.202676806612465</v>
       </c>
       <c r="D9">
-        <v>2.442203667916802</v>
+        <v>2.445076806612465</v>
       </c>
       <c r="E9">
-        <v>-2.882900000000001</v>
+        <v>-2.837600000000001</v>
       </c>
       <c r="F9">
-        <v>0.3171000000000001</v>
+        <v>0.3624000000000001</v>
       </c>
       <c r="G9">
         <v>2.12</v>
@@ -2522,28 +2522,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M9">
-        <v>0.01595013</v>
+        <v>0.01822872</v>
       </c>
       <c r="N9">
-        <v>0.5887165366666667</v>
+        <v>0.5864379466666667</v>
       </c>
       <c r="O9">
-        <v>0.09713822855000001</v>
+        <v>0.0967622612</v>
       </c>
       <c r="P9">
-        <v>0.4915783081166667</v>
+        <v>0.4896756854666667</v>
       </c>
       <c r="Q9">
-        <v>0.7385783081166667</v>
+        <v>0.7366756854666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08938456598992064</v>
+        <v>0.08978476560637749</v>
       </c>
       <c r="T9">
-        <v>0.8495443150535699</v>
+        <v>0.8573449504694682</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.90982685825549</v>
+        <v>33.17109850097355</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2568,22 +2568,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08596202435786729</v>
+        <v>0.0858563673451084</v>
       </c>
       <c r="C10">
-        <v>4.202676806612465</v>
+        <v>4.160256713497897</v>
       </c>
       <c r="D10">
-        <v>2.445076806612465</v>
+        <v>2.447956713497897</v>
       </c>
       <c r="E10">
-        <v>-2.837600000000001</v>
+        <v>-2.7923</v>
       </c>
       <c r="F10">
-        <v>0.3624000000000001</v>
+        <v>0.4077000000000001</v>
       </c>
       <c r="G10">
         <v>2.12</v>
@@ -2604,28 +2604,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M10">
-        <v>0.01822872</v>
+        <v>0.02050731</v>
       </c>
       <c r="N10">
-        <v>0.5864379466666667</v>
+        <v>0.5841593566666667</v>
       </c>
       <c r="O10">
-        <v>0.0967622612</v>
+        <v>0.09638629385000001</v>
       </c>
       <c r="P10">
-        <v>0.4896756854666667</v>
+        <v>0.4877730628166667</v>
       </c>
       <c r="Q10">
-        <v>0.7366756854666667</v>
+        <v>0.7347730628166667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08978476560637749</v>
+        <v>0.09019376081880044</v>
       </c>
       <c r="T10">
-        <v>0.8573449504694682</v>
+        <v>0.8653170284219799</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.17109850097355</v>
+        <v>29.48542088975427</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2650,22 +2650,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0858563673451084</v>
+        <v>0.0857507103323495</v>
       </c>
       <c r="C11">
-        <v>4.160256713497897</v>
+        <v>4.117843412516813</v>
       </c>
       <c r="D11">
-        <v>2.447956713497897</v>
+        <v>2.450843412516813</v>
       </c>
       <c r="E11">
-        <v>-2.7923</v>
+        <v>-2.747000000000001</v>
       </c>
       <c r="F11">
-        <v>0.4077000000000001</v>
+        <v>0.4530000000000001</v>
       </c>
       <c r="G11">
         <v>2.12</v>
@@ -2686,28 +2686,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M11">
-        <v>0.02050731</v>
+        <v>0.0227859</v>
       </c>
       <c r="N11">
-        <v>0.5841593566666667</v>
+        <v>0.5818807666666667</v>
       </c>
       <c r="O11">
-        <v>0.09638629385000001</v>
+        <v>0.09601032650000001</v>
       </c>
       <c r="P11">
-        <v>0.4877730628166667</v>
+        <v>0.4858704401666666</v>
       </c>
       <c r="Q11">
-        <v>0.7347730628166667</v>
+        <v>0.7328704401666666</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09019376081880044</v>
+        <v>0.09061184481372167</v>
       </c>
       <c r="T11">
-        <v>0.8653170284219799</v>
+        <v>0.8734662636623253</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.48542088975427</v>
+        <v>26.53687880077884</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2732,22 +2732,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0857507103323495</v>
+        <v>0.0856450533195906</v>
       </c>
       <c r="C12">
-        <v>4.117843412516813</v>
+        <v>4.075436927726003</v>
       </c>
       <c r="D12">
-        <v>2.450843412516813</v>
+        <v>2.453736927726003</v>
       </c>
       <c r="E12">
-        <v>-2.747</v>
+        <v>-2.701700000000001</v>
       </c>
       <c r="F12">
-        <v>0.4530000000000001</v>
+        <v>0.4983000000000001</v>
       </c>
       <c r="G12">
         <v>2.12</v>
@@ -2768,28 +2768,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M12">
-        <v>0.0227859</v>
+        <v>0.02506449000000001</v>
       </c>
       <c r="N12">
-        <v>0.5818807666666667</v>
+        <v>0.5796021766666667</v>
       </c>
       <c r="O12">
-        <v>0.09601032650000001</v>
+        <v>0.09563435915000001</v>
       </c>
       <c r="P12">
-        <v>0.4858704401666666</v>
+        <v>0.4839678175166667</v>
       </c>
       <c r="Q12">
-        <v>0.7328704401666666</v>
+        <v>0.7309678175166667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09061184481372167</v>
+        <v>0.09103932395459619</v>
       </c>
       <c r="T12">
-        <v>0.8734662636623253</v>
+        <v>0.881798627784476</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.53687880077884</v>
+        <v>24.12443527343531</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2814,22 +2814,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0856450533195906</v>
+        <v>0.0855393963068317</v>
       </c>
       <c r="C13">
-        <v>4.075436927726003</v>
+        <v>4.033037283295998</v>
       </c>
       <c r="D13">
-        <v>2.453736927726003</v>
+        <v>2.456637283295998</v>
       </c>
       <c r="E13">
-        <v>-2.701700000000001</v>
+        <v>-2.656400000000001</v>
       </c>
       <c r="F13">
-        <v>0.4983000000000001</v>
+        <v>0.5436000000000001</v>
       </c>
       <c r="G13">
         <v>2.12</v>
@@ -2850,28 +2850,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M13">
-        <v>0.02506449000000001</v>
+        <v>0.02734308</v>
       </c>
       <c r="N13">
-        <v>0.5796021766666667</v>
+        <v>0.5773235866666667</v>
       </c>
       <c r="O13">
-        <v>0.09563435915000001</v>
+        <v>0.09525839180000001</v>
       </c>
       <c r="P13">
-        <v>0.4839678175166667</v>
+        <v>0.4820651948666667</v>
       </c>
       <c r="Q13">
-        <v>0.7309678175166667</v>
+        <v>0.7290651948666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09103932395459619</v>
+        <v>0.09147651853049057</v>
       </c>
       <c r="T13">
-        <v>0.881798627784476</v>
+        <v>0.8903203638184938</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.12443527343531</v>
+        <v>22.1140656673157</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2896,22 +2896,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0855393963068317</v>
+        <v>0.0854337392940728</v>
       </c>
       <c r="C14">
-        <v>4.033037283295998</v>
+        <v>3.990644503511746</v>
       </c>
       <c r="D14">
-        <v>2.456637283295998</v>
+        <v>2.459544503511746</v>
       </c>
       <c r="E14">
-        <v>-2.656400000000001</v>
+        <v>-2.6111</v>
       </c>
       <c r="F14">
-        <v>0.5436000000000001</v>
+        <v>0.5889000000000002</v>
       </c>
       <c r="G14">
         <v>2.12</v>
@@ -2932,28 +2932,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M14">
-        <v>0.02734308</v>
+        <v>0.02962167000000001</v>
       </c>
       <c r="N14">
-        <v>0.5773235866666667</v>
+        <v>0.5750449966666666</v>
       </c>
       <c r="O14">
-        <v>0.09525839180000001</v>
+        <v>0.09488242445</v>
       </c>
       <c r="P14">
-        <v>0.4820651948666667</v>
+        <v>0.4801625722166666</v>
       </c>
       <c r="Q14">
-        <v>0.7290651948666667</v>
+        <v>0.7271625722166666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09147651853049057</v>
+        <v>0.09192376355640552</v>
       </c>
       <c r="T14">
-        <v>0.8903203638184938</v>
+        <v>0.8990380018303051</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.1140656673157</v>
+        <v>20.4129836929068</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2978,22 +2978,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0854337392940728</v>
+        <v>0.08532808228131392</v>
       </c>
       <c r="C15">
-        <v>3.990644503511746</v>
+        <v>3.948258612773285</v>
       </c>
       <c r="D15">
-        <v>2.459544503511746</v>
+        <v>2.462458612773285</v>
       </c>
       <c r="E15">
-        <v>-2.6111</v>
+        <v>-2.5658</v>
       </c>
       <c r="F15">
-        <v>0.5889000000000002</v>
+        <v>0.6342000000000002</v>
       </c>
       <c r="G15">
         <v>2.12</v>
@@ -3014,28 +3014,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M15">
-        <v>0.02962167000000001</v>
+        <v>0.03190026000000001</v>
       </c>
       <c r="N15">
-        <v>0.5750449966666666</v>
+        <v>0.5727664066666667</v>
       </c>
       <c r="O15">
-        <v>0.09488242445</v>
+        <v>0.09450645710000001</v>
       </c>
       <c r="P15">
-        <v>0.4801625722166666</v>
+        <v>0.4782599495666667</v>
       </c>
       <c r="Q15">
-        <v>0.7271625722166666</v>
+        <v>0.7252599495666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09192376355640552</v>
+        <v>0.09238140962943478</v>
       </c>
       <c r="T15">
-        <v>0.8990380018303051</v>
+        <v>0.9079583756098332</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.4129836929068</v>
+        <v>18.95491342912774</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3060,22 +3060,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08532808228131392</v>
+        <v>0.08522242526855502</v>
       </c>
       <c r="C16">
-        <v>3.948258612773285</v>
+        <v>3.905879635596432</v>
       </c>
       <c r="D16">
-        <v>2.462458612773285</v>
+        <v>2.465379635596432</v>
       </c>
       <c r="E16">
-        <v>-2.5658</v>
+        <v>-2.5205</v>
       </c>
       <c r="F16">
-        <v>0.6342000000000002</v>
+        <v>0.6795000000000003</v>
       </c>
       <c r="G16">
         <v>2.12</v>
@@ -3096,28 +3096,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M16">
-        <v>0.03190026000000001</v>
+        <v>0.03417885000000002</v>
       </c>
       <c r="N16">
-        <v>0.5727664066666667</v>
+        <v>0.5704878166666667</v>
       </c>
       <c r="O16">
-        <v>0.09450645710000001</v>
+        <v>0.09413048975</v>
       </c>
       <c r="P16">
-        <v>0.4782599495666667</v>
+        <v>0.4763573269166667</v>
       </c>
       <c r="Q16">
-        <v>0.7252599495666667</v>
+        <v>0.7233573269166667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09238140962943478</v>
+        <v>0.09284982384535884</v>
       </c>
       <c r="T16">
-        <v>0.9079583756098332</v>
+        <v>0.9170886405371147</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.95491342912774</v>
+        <v>17.69125253385256</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3142,22 +3142,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08522242526855502</v>
+        <v>0.0851167682557961</v>
       </c>
       <c r="C17">
-        <v>3.905879635596432</v>
+        <v>3.863507596613465</v>
       </c>
       <c r="D17">
-        <v>2.465379635596432</v>
+        <v>2.468307596613465</v>
       </c>
       <c r="E17">
-        <v>-2.520500000000001</v>
+        <v>-2.475200000000001</v>
       </c>
       <c r="F17">
-        <v>0.6795000000000001</v>
+        <v>0.7248000000000002</v>
       </c>
       <c r="G17">
         <v>2.12</v>
@@ -3178,28 +3178,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M17">
-        <v>0.03417885</v>
+        <v>0.03645744000000001</v>
       </c>
       <c r="N17">
-        <v>0.5704878166666667</v>
+        <v>0.5682092266666667</v>
       </c>
       <c r="O17">
-        <v>0.09413048975</v>
+        <v>0.09375452240000001</v>
       </c>
       <c r="P17">
-        <v>0.4763573269166667</v>
+        <v>0.4744547042666667</v>
       </c>
       <c r="Q17">
-        <v>0.7233573269166667</v>
+        <v>0.7214547042666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09284982384535884</v>
+        <v>0.09332939078070965</v>
       </c>
       <c r="T17">
-        <v>0.9170886405371147</v>
+        <v>0.9264362927245695</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.69125253385256</v>
+        <v>16.58554925048678</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3224,22 +3224,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0851167682557961</v>
+        <v>0.08501111124303722</v>
       </c>
       <c r="C18">
-        <v>3.863507596613465</v>
+        <v>3.821142520573814</v>
       </c>
       <c r="D18">
-        <v>2.468307596613465</v>
+        <v>2.471242520573815</v>
       </c>
       <c r="E18">
-        <v>-2.475200000000001</v>
+        <v>-2.4299</v>
       </c>
       <c r="F18">
-        <v>0.7248000000000002</v>
+        <v>0.7701000000000002</v>
       </c>
       <c r="G18">
         <v>2.12</v>
@@ -3260,28 +3260,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M18">
-        <v>0.03645744000000001</v>
+        <v>0.03873603000000001</v>
       </c>
       <c r="N18">
-        <v>0.5682092266666667</v>
+        <v>0.5659306366666667</v>
       </c>
       <c r="O18">
-        <v>0.09375452240000001</v>
+        <v>0.09337855505000001</v>
       </c>
       <c r="P18">
-        <v>0.4744547042666667</v>
+        <v>0.4725520816166666</v>
       </c>
       <c r="Q18">
-        <v>0.7214547042666667</v>
+        <v>0.7195520816166666</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09332939078070965</v>
+        <v>0.09382051354582797</v>
       </c>
       <c r="T18">
-        <v>0.9264362927245695</v>
+        <v>0.9360091895430475</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.58554925048678</v>
+        <v>15.60992870634049</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3306,22 +3306,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08501111124303722</v>
+        <v>0.08490545423027833</v>
       </c>
       <c r="C19">
-        <v>3.821142520573814</v>
+        <v>3.77878443234477</v>
       </c>
       <c r="D19">
-        <v>2.471242520573815</v>
+        <v>2.474184432344769</v>
       </c>
       <c r="E19">
-        <v>-2.4299</v>
+        <v>-2.3846</v>
       </c>
       <c r="F19">
-        <v>0.7701000000000002</v>
+        <v>0.8154000000000003</v>
       </c>
       <c r="G19">
         <v>2.12</v>
@@ -3342,28 +3342,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M19">
-        <v>0.03873603000000001</v>
+        <v>0.04101462000000002</v>
       </c>
       <c r="N19">
-        <v>0.5659306366666667</v>
+        <v>0.5636520466666667</v>
       </c>
       <c r="O19">
-        <v>0.09337855505000001</v>
+        <v>0.09300258770000001</v>
       </c>
       <c r="P19">
-        <v>0.4725520816166666</v>
+        <v>0.4706494589666667</v>
       </c>
       <c r="Q19">
-        <v>0.7195520816166666</v>
+        <v>0.7176494589666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09382051354582797</v>
+        <v>0.09432361491497357</v>
       </c>
       <c r="T19">
-        <v>0.9360091895430475</v>
+        <v>0.9458155716497809</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.60992870634049</v>
+        <v>14.74271044487713</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3388,22 +3388,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08490545423027834</v>
+        <v>0.08479979721751943</v>
       </c>
       <c r="C20">
-        <v>3.778784432344769</v>
+        <v>3.73643335691217</v>
       </c>
       <c r="D20">
-        <v>2.474184432344769</v>
+        <v>2.47713335691217</v>
       </c>
       <c r="E20">
-        <v>-2.384600000000001</v>
+        <v>-2.339300000000001</v>
       </c>
       <c r="F20">
-        <v>0.8154000000000001</v>
+        <v>0.8607000000000002</v>
       </c>
       <c r="G20">
         <v>2.12</v>
@@ -3424,28 +3424,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M20">
-        <v>0.04101462</v>
+        <v>0.04329321000000001</v>
       </c>
       <c r="N20">
-        <v>0.5636520466666667</v>
+        <v>0.5613734566666667</v>
       </c>
       <c r="O20">
-        <v>0.09300258770000001</v>
+        <v>0.09262662035000001</v>
       </c>
       <c r="P20">
-        <v>0.4706494589666667</v>
+        <v>0.4687468363166667</v>
       </c>
       <c r="Q20">
-        <v>0.7176494589666667</v>
+        <v>0.7157468363166667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09432361491497357</v>
+        <v>0.09483913854014743</v>
       </c>
       <c r="T20">
-        <v>0.9458155716497809</v>
+        <v>0.9558640866480386</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.74271044487713</v>
+        <v>13.96677831619939</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3470,22 +3470,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08479979721751943</v>
+        <v>0.08469414020476052</v>
       </c>
       <c r="C21">
-        <v>3.73643335691217</v>
+        <v>3.69408931938112</v>
       </c>
       <c r="D21">
-        <v>2.47713335691217</v>
+        <v>2.48008931938112</v>
       </c>
       <c r="E21">
-        <v>-2.339300000000001</v>
+        <v>-2.294</v>
       </c>
       <c r="F21">
-        <v>0.8607000000000002</v>
+        <v>0.9060000000000002</v>
       </c>
       <c r="G21">
         <v>2.12</v>
@@ -3506,28 +3506,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M21">
-        <v>0.04329321000000001</v>
+        <v>0.04557180000000001</v>
       </c>
       <c r="N21">
-        <v>0.5613734566666667</v>
+        <v>0.5590948666666666</v>
       </c>
       <c r="O21">
-        <v>0.09262662035000001</v>
+        <v>0.092250653</v>
       </c>
       <c r="P21">
-        <v>0.4687468363166667</v>
+        <v>0.4668442136666666</v>
       </c>
       <c r="Q21">
-        <v>0.7157468363166667</v>
+        <v>0.7138442136666666</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09483913854014743</v>
+        <v>0.09536755025595064</v>
       </c>
       <c r="T21">
-        <v>0.9558640866480386</v>
+        <v>0.9661638145212527</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.96677831619939</v>
+        <v>13.26843940038942</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3552,22 +3552,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08469414020476052</v>
+        <v>0.08485150819200162</v>
       </c>
       <c r="C22">
-        <v>3.69408931938112</v>
+        <v>3.64438920755477</v>
       </c>
       <c r="D22">
-        <v>2.48008931938112</v>
+        <v>2.47568920755477</v>
       </c>
       <c r="E22">
-        <v>-2.294</v>
+        <v>-2.2487</v>
       </c>
       <c r="F22">
-        <v>0.9060000000000002</v>
+        <v>0.9513000000000004</v>
       </c>
       <c r="G22">
         <v>2.12</v>
@@ -3588,45 +3588,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M22">
-        <v>0.04557180000000001</v>
+        <v>0.04927734000000002</v>
       </c>
       <c r="N22">
-        <v>0.5590948666666666</v>
+        <v>0.5553893266666666</v>
       </c>
       <c r="O22">
-        <v>0.092250653</v>
+        <v>0.0916392389</v>
       </c>
       <c r="P22">
-        <v>0.4668442136666666</v>
+        <v>0.4637500877666666</v>
       </c>
       <c r="Q22">
-        <v>0.7138442136666666</v>
+        <v>0.7107500877666666</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09536755025595064</v>
+        <v>0.09590933948354635</v>
       </c>
       <c r="T22">
-        <v>0.9661638145212527</v>
+        <v>0.9767242949988519</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.165</v>
       </c>
       <c r="W22">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.26843940038942</v>
+        <v>12.27068398307754</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3634,22 +3634,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08485150819200162</v>
+        <v>0.08475837617924271</v>
       </c>
       <c r="C23">
-        <v>3.64438920755477</v>
+        <v>3.601691351709382</v>
       </c>
       <c r="D23">
-        <v>2.47568920755477</v>
+        <v>2.478291351709382</v>
       </c>
       <c r="E23">
-        <v>-2.2487</v>
+        <v>-2.2034</v>
       </c>
       <c r="F23">
-        <v>0.9513000000000003</v>
+        <v>0.9966000000000003</v>
       </c>
       <c r="G23">
         <v>2.12</v>
@@ -3670,28 +3670,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M23">
-        <v>0.04927734000000001</v>
+        <v>0.05162388000000001</v>
       </c>
       <c r="N23">
-        <v>0.5553893266666666</v>
+        <v>0.5530427866666667</v>
       </c>
       <c r="O23">
-        <v>0.0916392389</v>
+        <v>0.09125205980000002</v>
       </c>
       <c r="P23">
-        <v>0.4637500877666666</v>
+        <v>0.4617907268666667</v>
       </c>
       <c r="Q23">
-        <v>0.7107500877666666</v>
+        <v>0.7087907268666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09590933948354635</v>
+        <v>0.09646502074261887</v>
       </c>
       <c r="T23">
-        <v>0.9767242949988519</v>
+        <v>0.987555557027159</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.27068398307755</v>
+        <v>11.71292562021039</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3716,22 +3716,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08475837617924271</v>
+        <v>0.08466524416648381</v>
       </c>
       <c r="C24">
-        <v>3.601691351709382</v>
+        <v>3.558998971736075</v>
       </c>
       <c r="D24">
-        <v>2.478291351709382</v>
+        <v>2.480898971736075</v>
       </c>
       <c r="E24">
-        <v>-2.2034</v>
+        <v>-2.1581</v>
       </c>
       <c r="F24">
-        <v>0.9966000000000003</v>
+        <v>1.0419</v>
       </c>
       <c r="G24">
         <v>2.12</v>
@@ -3752,28 +3752,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M24">
-        <v>0.05162388000000001</v>
+        <v>0.05397042000000001</v>
       </c>
       <c r="N24">
-        <v>0.5530427866666667</v>
+        <v>0.5506962466666667</v>
       </c>
       <c r="O24">
-        <v>0.09125205980000002</v>
+        <v>0.09086488070000001</v>
       </c>
       <c r="P24">
-        <v>0.4617907268666667</v>
+        <v>0.4598313659666667</v>
       </c>
       <c r="Q24">
-        <v>0.7087907268666667</v>
+        <v>0.7068313659666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09646502074261887</v>
+        <v>0.09703513528114782</v>
       </c>
       <c r="T24">
-        <v>0.987555557027159</v>
+        <v>0.9986681505367208</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.71292562021039</v>
+        <v>11.20366798454907</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3798,22 +3798,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08466524416648381</v>
+        <v>0.08457211215372491</v>
       </c>
       <c r="C25">
-        <v>3.558998971736075</v>
+        <v>3.516312084937938</v>
       </c>
       <c r="D25">
-        <v>2.480898971736075</v>
+        <v>2.483512084937938</v>
       </c>
       <c r="E25">
-        <v>-2.1581</v>
+        <v>-2.1128</v>
       </c>
       <c r="F25">
-        <v>1.0419</v>
+        <v>1.0872</v>
       </c>
       <c r="G25">
         <v>2.12</v>
@@ -3834,28 +3834,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M25">
-        <v>0.05397042000000001</v>
+        <v>0.05631696000000002</v>
       </c>
       <c r="N25">
-        <v>0.5506962466666667</v>
+        <v>0.5483497066666667</v>
       </c>
       <c r="O25">
-        <v>0.09086488070000001</v>
+        <v>0.09047770160000002</v>
       </c>
       <c r="P25">
-        <v>0.4598313659666667</v>
+        <v>0.4578720050666667</v>
       </c>
       <c r="Q25">
-        <v>0.7068313659666667</v>
+        <v>0.7048720050666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09703513528114782</v>
+        <v>0.09762025283384858</v>
       </c>
       <c r="T25">
-        <v>0.9986681505367208</v>
+        <v>1.010073180717587</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.20366798454907</v>
+        <v>10.73684848519285</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3880,22 +3880,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08457211215372491</v>
+        <v>0.08447898014096603</v>
       </c>
       <c r="C26">
-        <v>3.516312084937938</v>
+        <v>3.473630708691042</v>
       </c>
       <c r="D26">
-        <v>2.483512084937938</v>
+        <v>2.486130708691042</v>
       </c>
       <c r="E26">
-        <v>-2.1128</v>
+        <v>-2.0675</v>
       </c>
       <c r="F26">
-        <v>1.0872</v>
+        <v>1.1325</v>
       </c>
       <c r="G26">
         <v>2.12</v>
@@ -3916,28 +3916,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M26">
-        <v>0.05631696000000001</v>
+        <v>0.05866350000000001</v>
       </c>
       <c r="N26">
-        <v>0.5483497066666667</v>
+        <v>0.5460031666666667</v>
       </c>
       <c r="O26">
-        <v>0.09047770160000002</v>
+        <v>0.09009052250000001</v>
       </c>
       <c r="P26">
-        <v>0.4578720050666667</v>
+        <v>0.4559126441666667</v>
       </c>
       <c r="Q26">
-        <v>0.7048720050666667</v>
+        <v>0.7029126441666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09762025283384858</v>
+        <v>0.09822097352128803</v>
       </c>
       <c r="T26">
-        <v>1.010073180717587</v>
+        <v>1.021782345036609</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.73684848519285</v>
+        <v>10.30737454578514</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3962,22 +3962,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08447898014096603</v>
+        <v>0.08438584812820712</v>
       </c>
       <c r="C27">
-        <v>3.473630708691042</v>
+        <v>3.430954860444817</v>
       </c>
       <c r="D27">
-        <v>2.486130708691042</v>
+        <v>2.488754860444817</v>
       </c>
       <c r="E27">
-        <v>-2.0675</v>
+        <v>-2.0222</v>
       </c>
       <c r="F27">
-        <v>1.1325</v>
+        <v>1.1778</v>
       </c>
       <c r="G27">
         <v>2.12</v>
@@ -3998,28 +3998,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M27">
-        <v>0.05866350000000001</v>
+        <v>0.06101004000000002</v>
       </c>
       <c r="N27">
-        <v>0.5460031666666667</v>
+        <v>0.5436566266666667</v>
       </c>
       <c r="O27">
-        <v>0.09009052250000001</v>
+        <v>0.08970334340000001</v>
       </c>
       <c r="P27">
-        <v>0.4559126441666667</v>
+        <v>0.4539532832666667</v>
       </c>
       <c r="Q27">
-        <v>0.7029126441666667</v>
+        <v>0.7009532832666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09822097352128803</v>
+        <v>0.09883792990298261</v>
       </c>
       <c r="T27">
-        <v>1.021782345036609</v>
+        <v>1.033807973256146</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.30737454578514</v>
+        <v>9.910937063254941</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4044,22 +4044,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08438584812820712</v>
+        <v>0.08467598111544823</v>
       </c>
       <c r="C28">
-        <v>3.430954860444817</v>
+        <v>3.377498066152156</v>
       </c>
       <c r="D28">
-        <v>2.488754860444817</v>
+        <v>2.480598066152156</v>
       </c>
       <c r="E28">
-        <v>-2.0222</v>
+        <v>-1.9769</v>
       </c>
       <c r="F28">
-        <v>1.1778</v>
+        <v>1.2231</v>
       </c>
       <c r="G28">
         <v>2.12</v>
@@ -4080,45 +4080,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M28">
-        <v>0.06101004000000002</v>
+        <v>0.06543585000000002</v>
       </c>
       <c r="N28">
-        <v>0.5436566266666667</v>
+        <v>0.5392308166666666</v>
       </c>
       <c r="O28">
-        <v>0.08970334340000001</v>
+        <v>0.08897308475</v>
       </c>
       <c r="P28">
-        <v>0.4539532832666667</v>
+        <v>0.4502577319166666</v>
       </c>
       <c r="Q28">
-        <v>0.7009532832666667</v>
+        <v>0.6972577319166666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09883792990298261</v>
+        <v>0.09947178919924415</v>
       </c>
       <c r="T28">
-        <v>1.033807973256146</v>
+        <v>1.046163070741971</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.165</v>
       </c>
       <c r="W28">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>9.910937063254941</v>
+        <v>9.240602309997753</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4126,22 +4126,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08467598111544823</v>
+        <v>0.08459704410268934</v>
       </c>
       <c r="C29">
-        <v>3.377498066152156</v>
+        <v>3.334412000826881</v>
       </c>
       <c r="D29">
-        <v>2.480598066152156</v>
+        <v>2.482812000826881</v>
       </c>
       <c r="E29">
-        <v>-1.9769</v>
+        <v>-1.9316</v>
       </c>
       <c r="F29">
-        <v>1.2231</v>
+        <v>1.2684</v>
       </c>
       <c r="G29">
         <v>2.12</v>
@@ -4162,28 +4162,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M29">
-        <v>0.06543585000000002</v>
+        <v>0.06785940000000001</v>
       </c>
       <c r="N29">
-        <v>0.5392308166666666</v>
+        <v>0.5368072666666667</v>
       </c>
       <c r="O29">
-        <v>0.08897308475</v>
+        <v>0.08857319900000001</v>
       </c>
       <c r="P29">
-        <v>0.4502577319166666</v>
+        <v>0.4482340676666667</v>
       </c>
       <c r="Q29">
-        <v>0.6972577319166666</v>
+        <v>0.6952340676666666</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09947178919924415</v>
+        <v>0.1001232556981796</v>
       </c>
       <c r="T29">
-        <v>1.046163070741971</v>
+        <v>1.05886136538018</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.240602309997753</v>
+        <v>8.910580798926407</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4208,22 +4208,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08459704410268934</v>
+        <v>0.08451810708993042</v>
       </c>
       <c r="C30">
-        <v>3.334412000826881</v>
+        <v>3.291329890906808</v>
       </c>
       <c r="D30">
-        <v>2.482812000826881</v>
+        <v>2.485029890906809</v>
       </c>
       <c r="E30">
-        <v>-1.9316</v>
+        <v>-1.8863</v>
       </c>
       <c r="F30">
-        <v>1.2684</v>
+        <v>1.313700000000001</v>
       </c>
       <c r="G30">
         <v>2.12</v>
@@ -4244,28 +4244,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M30">
-        <v>0.06785940000000001</v>
+        <v>0.07028295000000002</v>
       </c>
       <c r="N30">
-        <v>0.5368072666666667</v>
+        <v>0.5343837166666666</v>
       </c>
       <c r="O30">
-        <v>0.08857319900000001</v>
+        <v>0.08817331325</v>
       </c>
       <c r="P30">
-        <v>0.4482340676666667</v>
+        <v>0.4462104034166666</v>
       </c>
       <c r="Q30">
-        <v>0.6952340676666666</v>
+        <v>0.6932104034166666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1001232556981796</v>
+        <v>0.1007930733660992</v>
       </c>
       <c r="T30">
-        <v>1.05886136538018</v>
+        <v>1.071917358458902</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.910580798926407</v>
+        <v>8.603319392066872</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4290,22 +4290,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08451810708993042</v>
+        <v>0.08443917007717153</v>
       </c>
       <c r="C31">
-        <v>3.291329890906808</v>
+        <v>3.248251747001479</v>
       </c>
       <c r="D31">
-        <v>2.485029890906809</v>
+        <v>2.487251747001479</v>
       </c>
       <c r="E31">
-        <v>-1.8863</v>
+        <v>-1.841</v>
       </c>
       <c r="F31">
-        <v>1.3137</v>
+        <v>1.359</v>
       </c>
       <c r="G31">
         <v>2.12</v>
@@ -4326,28 +4326,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M31">
-        <v>0.07028295000000001</v>
+        <v>0.07270650000000001</v>
       </c>
       <c r="N31">
-        <v>0.5343837166666667</v>
+        <v>0.5319601666666667</v>
       </c>
       <c r="O31">
-        <v>0.08817331325000001</v>
+        <v>0.0877734275</v>
       </c>
       <c r="P31">
-        <v>0.4462104034166667</v>
+        <v>0.4441867391666667</v>
       </c>
       <c r="Q31">
-        <v>0.6932104034166667</v>
+        <v>0.6911867391666666</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1007930733660992</v>
+        <v>0.1014820286816736</v>
       </c>
       <c r="T31">
-        <v>1.071917358458902</v>
+        <v>1.085346379911302</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -4364,7 +4364,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.603319392066876</v>
+        <v>8.31654207899798</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4372,22 +4372,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08443917007717153</v>
+        <v>0.08436023306441263</v>
       </c>
       <c r="C32">
-        <v>3.248251747001479</v>
+        <v>3.205177579758408</v>
       </c>
       <c r="D32">
-        <v>2.487251747001479</v>
+        <v>2.489477579758408</v>
       </c>
       <c r="E32">
-        <v>-1.841</v>
+        <v>-1.7957</v>
       </c>
       <c r="F32">
-        <v>1.359</v>
+        <v>1.4043</v>
       </c>
       <c r="G32">
         <v>2.12</v>
@@ -4408,28 +4408,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M32">
-        <v>0.07270650000000001</v>
+        <v>0.07513005000000002</v>
       </c>
       <c r="N32">
-        <v>0.5319601666666667</v>
+        <v>0.5295366166666666</v>
       </c>
       <c r="O32">
-        <v>0.0877734275</v>
+        <v>0.08737354174999999</v>
       </c>
       <c r="P32">
-        <v>0.4441867391666667</v>
+        <v>0.4421630749166666</v>
       </c>
       <c r="Q32">
-        <v>0.6911867391666666</v>
+        <v>0.6891630749166666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1014820286816736</v>
+        <v>0.1021909537165401</v>
       </c>
       <c r="T32">
-        <v>1.085346379911302</v>
+        <v>1.099164648362323</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.31654207899798</v>
+        <v>8.048266528062559</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4454,22 +4454,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08436023306441263</v>
+        <v>0.08428129605165373</v>
       </c>
       <c r="C33">
-        <v>3.205177579758408</v>
+        <v>3.162107399863263</v>
       </c>
       <c r="D33">
-        <v>2.489477579758408</v>
+        <v>2.491707399863264</v>
       </c>
       <c r="E33">
-        <v>-1.7957</v>
+        <v>-1.7504</v>
       </c>
       <c r="F33">
-        <v>1.4043</v>
+        <v>1.4496</v>
       </c>
       <c r="G33">
         <v>2.12</v>
@@ -4490,28 +4490,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M33">
-        <v>0.07513005000000002</v>
+        <v>0.07755360000000003</v>
       </c>
       <c r="N33">
-        <v>0.5295366166666666</v>
+        <v>0.5271130666666667</v>
       </c>
       <c r="O33">
-        <v>0.08737354174999999</v>
+        <v>0.08697365600000001</v>
       </c>
       <c r="P33">
-        <v>0.4421630749166666</v>
+        <v>0.4401394106666667</v>
       </c>
       <c r="Q33">
-        <v>0.6891630749166666</v>
+        <v>0.6871394106666666</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1021909537165401</v>
+        <v>0.1029207294877261</v>
       </c>
       <c r="T33">
-        <v>1.099164648362323</v>
+        <v>1.113389336473667</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.048266528062559</v>
+        <v>7.796758199060604</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4536,22 +4536,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08428129605165373</v>
+        <v>0.08442279903889484</v>
       </c>
       <c r="C34">
-        <v>3.162107399863263</v>
+        <v>3.112813043470241</v>
       </c>
       <c r="D34">
-        <v>2.491707399863264</v>
+        <v>2.487713043470241</v>
       </c>
       <c r="E34">
-        <v>-1.7504</v>
+        <v>-1.7051</v>
       </c>
       <c r="F34">
-        <v>1.4496</v>
+        <v>1.4949</v>
       </c>
       <c r="G34">
         <v>2.12</v>
@@ -4572,45 +4572,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M34">
-        <v>0.07755360000000003</v>
+        <v>0.08117307000000001</v>
       </c>
       <c r="N34">
-        <v>0.5271130666666667</v>
+        <v>0.5234935966666667</v>
       </c>
       <c r="O34">
-        <v>0.08697365600000001</v>
+        <v>0.08637644345000002</v>
       </c>
       <c r="P34">
-        <v>0.4401394106666667</v>
+        <v>0.4371171532166667</v>
       </c>
       <c r="Q34">
-        <v>0.6871394106666666</v>
+        <v>0.6841171532166668</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1029207294877261</v>
+        <v>0.1036722896102908</v>
       </c>
       <c r="T34">
-        <v>1.113389336473667</v>
+        <v>1.128038642140574</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.165</v>
       </c>
       <c r="W34">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.796758199060604</v>
+        <v>7.449104323227724</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4618,22 +4618,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08442279903889484</v>
+        <v>0.08435054202613593</v>
       </c>
       <c r="C35">
-        <v>3.112813043470241</v>
+        <v>3.069551118183872</v>
       </c>
       <c r="D35">
-        <v>2.487713043470241</v>
+        <v>2.489751118183872</v>
       </c>
       <c r="E35">
-        <v>-1.7051</v>
+        <v>-1.6598</v>
       </c>
       <c r="F35">
-        <v>1.4949</v>
+        <v>1.5402</v>
       </c>
       <c r="G35">
         <v>2.12</v>
@@ -4654,28 +4654,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M35">
-        <v>0.08117307000000001</v>
+        <v>0.08363286000000003</v>
       </c>
       <c r="N35">
-        <v>0.5234935966666667</v>
+        <v>0.5210338066666667</v>
       </c>
       <c r="O35">
-        <v>0.08637644345000002</v>
+        <v>0.0859705781</v>
       </c>
       <c r="P35">
-        <v>0.4371171532166667</v>
+        <v>0.4350632285666667</v>
       </c>
       <c r="Q35">
-        <v>0.6841171532166668</v>
+        <v>0.6820632285666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1036722896102908</v>
+        <v>0.1044466242820242</v>
       </c>
       <c r="T35">
-        <v>1.128038642140574</v>
+        <v>1.143131866161023</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.449104323227724</v>
+        <v>7.230013019603377</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4700,22 +4700,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08435054202613593</v>
+        <v>0.08427828501337703</v>
       </c>
       <c r="C36">
-        <v>3.069551118183872</v>
+        <v>3.026292535046891</v>
       </c>
       <c r="D36">
-        <v>2.489751118183872</v>
+        <v>2.491792535046891</v>
       </c>
       <c r="E36">
-        <v>-1.6598</v>
+        <v>-1.6145</v>
       </c>
       <c r="F36">
-        <v>1.5402</v>
+        <v>1.585500000000001</v>
       </c>
       <c r="G36">
         <v>2.12</v>
@@ -4736,28 +4736,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M36">
-        <v>0.08363286000000003</v>
+        <v>0.08609265000000003</v>
       </c>
       <c r="N36">
-        <v>0.5210338066666667</v>
+        <v>0.5185740166666667</v>
       </c>
       <c r="O36">
-        <v>0.0859705781</v>
+        <v>0.08556471275000001</v>
       </c>
       <c r="P36">
-        <v>0.4350632285666667</v>
+        <v>0.4330093039166667</v>
       </c>
       <c r="Q36">
-        <v>0.6820632285666667</v>
+        <v>0.6800093039166667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1044466242820242</v>
+        <v>0.1052447846359647</v>
       </c>
       <c r="T36">
-        <v>1.143131866161023</v>
+        <v>1.15868949707441</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.230013019603377</v>
+        <v>7.02344121904328</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4782,22 +4782,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08427828501337703</v>
+        <v>0.08420602800061813</v>
       </c>
       <c r="C37">
-        <v>3.026292535046891</v>
+        <v>2.983037302287011</v>
       </c>
       <c r="D37">
-        <v>2.491792535046891</v>
+        <v>2.493837302287012</v>
       </c>
       <c r="E37">
-        <v>-1.6145</v>
+        <v>-1.5692</v>
       </c>
       <c r="F37">
-        <v>1.585500000000001</v>
+        <v>1.630800000000001</v>
       </c>
       <c r="G37">
         <v>2.12</v>
@@ -4818,28 +4818,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M37">
-        <v>0.08609265000000003</v>
+        <v>0.08855244000000004</v>
       </c>
       <c r="N37">
-        <v>0.5185740166666667</v>
+        <v>0.5161142266666666</v>
       </c>
       <c r="O37">
-        <v>0.08556471275000001</v>
+        <v>0.0851588474</v>
       </c>
       <c r="P37">
-        <v>0.4330093039166667</v>
+        <v>0.4309553792666666</v>
       </c>
       <c r="Q37">
-        <v>0.6800093039166667</v>
+        <v>0.6779553792666666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1052447846359647</v>
+        <v>0.1060678875009659</v>
       </c>
       <c r="T37">
-        <v>1.15868949707441</v>
+        <v>1.17473330395384</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.02344121904328</v>
+        <v>6.828345629625411</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4864,22 +4864,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08420602800061815</v>
+        <v>0.08413377098785924</v>
       </c>
       <c r="C38">
-        <v>2.983037302287011</v>
+        <v>2.939785428158973</v>
       </c>
       <c r="D38">
-        <v>2.493837302287011</v>
+        <v>2.495885428158974</v>
       </c>
       <c r="E38">
-        <v>-1.5692</v>
+        <v>-1.5239</v>
       </c>
       <c r="F38">
-        <v>1.6308</v>
+        <v>1.6761</v>
       </c>
       <c r="G38">
         <v>2.12</v>
@@ -4900,28 +4900,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M38">
-        <v>0.08855244000000001</v>
+        <v>0.09101223000000003</v>
       </c>
       <c r="N38">
-        <v>0.5161142266666667</v>
+        <v>0.5136544366666667</v>
       </c>
       <c r="O38">
-        <v>0.08515884740000002</v>
+        <v>0.08475298205000001</v>
       </c>
       <c r="P38">
-        <v>0.4309553792666667</v>
+        <v>0.4289014546166666</v>
       </c>
       <c r="Q38">
-        <v>0.6779553792666667</v>
+        <v>0.6759014546166666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1060678875009659</v>
+        <v>0.1069171206156496</v>
       </c>
       <c r="T38">
-        <v>1.17473330395384</v>
+        <v>1.191286438035791</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.828345629625414</v>
+        <v>6.643795747743644</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4946,22 +4946,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08413377098785924</v>
+        <v>0.08406151397510034</v>
       </c>
       <c r="C39">
-        <v>2.939785428158973</v>
+        <v>2.89653692094466</v>
       </c>
       <c r="D39">
-        <v>2.495885428158974</v>
+        <v>2.49793692094466</v>
       </c>
       <c r="E39">
-        <v>-1.5239</v>
+        <v>-1.4786</v>
       </c>
       <c r="F39">
-        <v>1.6761</v>
+        <v>1.7214</v>
       </c>
       <c r="G39">
         <v>2.12</v>
@@ -4982,28 +4982,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M39">
-        <v>0.09101223000000003</v>
+        <v>0.09347202000000003</v>
       </c>
       <c r="N39">
-        <v>0.5136544366666667</v>
+        <v>0.5111946466666667</v>
       </c>
       <c r="O39">
-        <v>0.08475298205000001</v>
+        <v>0.0843471167</v>
       </c>
       <c r="P39">
-        <v>0.4289014546166666</v>
+        <v>0.4268475299666667</v>
       </c>
       <c r="Q39">
-        <v>0.6759014546166666</v>
+        <v>0.6738475299666666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1069171206156496</v>
+        <v>0.107793748346936</v>
       </c>
       <c r="T39">
-        <v>1.191286438035791</v>
+        <v>1.208373544184902</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.643795747743644</v>
+        <v>6.468959017539864</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5028,22 +5028,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08406151397510034</v>
+        <v>0.08398925696234145</v>
       </c>
       <c r="C40">
-        <v>2.89653692094466</v>
+        <v>2.853291788953201</v>
       </c>
       <c r="D40">
-        <v>2.49793692094466</v>
+        <v>2.499991788953202</v>
       </c>
       <c r="E40">
-        <v>-1.4786</v>
+        <v>-1.4333</v>
       </c>
       <c r="F40">
-        <v>1.7214</v>
+        <v>1.766700000000001</v>
       </c>
       <c r="G40">
         <v>2.12</v>
@@ -5064,28 +5064,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M40">
-        <v>0.09347202000000003</v>
+        <v>0.09593181000000003</v>
       </c>
       <c r="N40">
-        <v>0.5111946466666667</v>
+        <v>0.5087348566666666</v>
       </c>
       <c r="O40">
-        <v>0.0843471167</v>
+        <v>0.08394125135</v>
       </c>
       <c r="P40">
-        <v>0.4268475299666667</v>
+        <v>0.4247936053166667</v>
       </c>
       <c r="Q40">
-        <v>0.6738475299666666</v>
+        <v>0.6717936053166667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.107793748346936</v>
+        <v>0.1086991179710516</v>
       </c>
       <c r="T40">
-        <v>1.208373544184902</v>
+        <v>1.226020883322508</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.468959017539864</v>
+        <v>6.303088273500379</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5110,22 +5110,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08398925696234145</v>
+        <v>0.08391699994958254</v>
       </c>
       <c r="C41">
-        <v>2.853291788953201</v>
+        <v>2.810050040521099</v>
       </c>
       <c r="D41">
-        <v>2.499991788953202</v>
+        <v>2.502050040521099</v>
       </c>
       <c r="E41">
-        <v>-1.4333</v>
+        <v>-1.388</v>
       </c>
       <c r="F41">
-        <v>1.766700000000001</v>
+        <v>1.812</v>
       </c>
       <c r="G41">
         <v>2.12</v>
@@ -5146,28 +5146,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M41">
-        <v>0.09593181000000003</v>
+        <v>0.09839160000000002</v>
       </c>
       <c r="N41">
-        <v>0.5087348566666666</v>
+        <v>0.5062750666666667</v>
       </c>
       <c r="O41">
-        <v>0.08394125135</v>
+        <v>0.083535386</v>
       </c>
       <c r="P41">
-        <v>0.4247936053166667</v>
+        <v>0.4227396806666667</v>
       </c>
       <c r="Q41">
-        <v>0.6717936053166667</v>
+        <v>0.6697396806666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1086991179710516</v>
+        <v>0.1096346665826376</v>
       </c>
       <c r="T41">
-        <v>1.226020883322508</v>
+        <v>1.244256467098035</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.303088273500379</v>
+        <v>6.145511066662871</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5192,22 +5192,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08391699994958254</v>
+        <v>0.08418709293682365</v>
       </c>
       <c r="C42">
-        <v>2.810050040521099</v>
+        <v>2.757073691808358</v>
       </c>
       <c r="D42">
-        <v>2.502050040521099</v>
+        <v>2.494373691808358</v>
       </c>
       <c r="E42">
-        <v>-1.388</v>
+        <v>-1.3427</v>
       </c>
       <c r="F42">
-        <v>1.812</v>
+        <v>1.857300000000001</v>
       </c>
       <c r="G42">
         <v>2.12</v>
@@ -5228,45 +5228,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M42">
-        <v>0.09839160000000002</v>
+        <v>0.10270869</v>
       </c>
       <c r="N42">
-        <v>0.5062750666666667</v>
+        <v>0.5019579766666666</v>
       </c>
       <c r="O42">
-        <v>0.083535386</v>
+        <v>0.08282306615</v>
       </c>
       <c r="P42">
-        <v>0.4227396806666667</v>
+        <v>0.4191349105166666</v>
       </c>
       <c r="Q42">
-        <v>0.6697396806666667</v>
+        <v>0.6661349105166666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1096346665826376</v>
+        <v>0.1106019287064808</v>
       </c>
       <c r="T42">
-        <v>1.244256467098035</v>
+        <v>1.263110206255783</v>
       </c>
       <c r="U42">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.165</v>
       </c>
       <c r="W42">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>6.145511066662871</v>
+        <v>5.887200651343781</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5274,22 +5274,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08418709293682365</v>
+        <v>0.08412318592406476</v>
       </c>
       <c r="C43">
-        <v>2.757073691808358</v>
+        <v>2.713585744457316</v>
       </c>
       <c r="D43">
-        <v>2.494373691808358</v>
+        <v>2.496185744457317</v>
       </c>
       <c r="E43">
-        <v>-1.3427</v>
+        <v>-1.2974</v>
       </c>
       <c r="F43">
-        <v>1.857300000000001</v>
+        <v>1.902600000000001</v>
       </c>
       <c r="G43">
         <v>2.12</v>
@@ -5310,28 +5310,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M43">
-        <v>0.10270869</v>
+        <v>0.10521378</v>
       </c>
       <c r="N43">
-        <v>0.5019579766666666</v>
+        <v>0.4994528866666667</v>
       </c>
       <c r="O43">
-        <v>0.08282306615</v>
+        <v>0.0824097263</v>
       </c>
       <c r="P43">
-        <v>0.4191349105166666</v>
+        <v>0.4170431603666667</v>
       </c>
       <c r="Q43">
-        <v>0.6661349105166666</v>
+        <v>0.6640431603666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1106019287064808</v>
+        <v>0.1116025446966634</v>
       </c>
       <c r="T43">
-        <v>1.263110206255783</v>
+        <v>1.282614074350005</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.887200651343781</v>
+        <v>5.747029207264166</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5356,22 +5356,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08412318592406476</v>
+        <v>0.08405927891130585</v>
       </c>
       <c r="C44">
-        <v>2.713585744457316</v>
+        <v>2.670100431773159</v>
       </c>
       <c r="D44">
-        <v>2.496185744457317</v>
+        <v>2.498000431773159</v>
       </c>
       <c r="E44">
-        <v>-1.2974</v>
+        <v>-1.2521</v>
       </c>
       <c r="F44">
-        <v>1.902600000000001</v>
+        <v>1.9479</v>
       </c>
       <c r="G44">
         <v>2.12</v>
@@ -5392,28 +5392,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M44">
-        <v>0.10521378</v>
+        <v>0.10771887</v>
       </c>
       <c r="N44">
-        <v>0.4994528866666667</v>
+        <v>0.4969477966666667</v>
       </c>
       <c r="O44">
-        <v>0.0824097263</v>
+        <v>0.08199638645</v>
       </c>
       <c r="P44">
-        <v>0.4170431603666667</v>
+        <v>0.4149514102166666</v>
       </c>
       <c r="Q44">
-        <v>0.6640431603666667</v>
+        <v>0.6619514102166666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1116025446966634</v>
+        <v>0.1126382700198348</v>
       </c>
       <c r="T44">
-        <v>1.282614074350005</v>
+        <v>1.302802288693147</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.747029207264167</v>
+        <v>5.613377365234768</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5438,22 +5438,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08405927891130585</v>
+        <v>0.08399537189854696</v>
       </c>
       <c r="C45">
-        <v>2.670100431773159</v>
+        <v>2.626617759506147</v>
       </c>
       <c r="D45">
-        <v>2.498000431773159</v>
+        <v>2.499817759506148</v>
       </c>
       <c r="E45">
-        <v>-1.2521</v>
+        <v>-1.2068</v>
       </c>
       <c r="F45">
-        <v>1.9479</v>
+        <v>1.993200000000001</v>
       </c>
       <c r="G45">
         <v>2.12</v>
@@ -5474,28 +5474,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M45">
-        <v>0.10771887</v>
+        <v>0.11022396</v>
       </c>
       <c r="N45">
-        <v>0.4969477966666667</v>
+        <v>0.4944427066666667</v>
       </c>
       <c r="O45">
-        <v>0.08199638645</v>
+        <v>0.0815830466</v>
       </c>
       <c r="P45">
-        <v>0.4149514102166666</v>
+        <v>0.4128596600666667</v>
       </c>
       <c r="Q45">
-        <v>0.6619514102166666</v>
+        <v>0.6598596600666666</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1126382700198348</v>
+        <v>0.1137109855331196</v>
       </c>
       <c r="T45">
-        <v>1.302802288693147</v>
+        <v>1.323711510691401</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.613377365234768</v>
+        <v>5.485800606933978</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5520,22 +5520,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08399537189854696</v>
+        <v>0.08393146488578808</v>
       </c>
       <c r="C46">
-        <v>2.626617759506147</v>
+        <v>2.583137733423291</v>
       </c>
       <c r="D46">
-        <v>2.499817759506148</v>
+        <v>2.501637733423291</v>
       </c>
       <c r="E46">
-        <v>-1.2068</v>
+        <v>-1.1615</v>
       </c>
       <c r="F46">
-        <v>1.993200000000001</v>
+        <v>2.0385</v>
       </c>
       <c r="G46">
         <v>2.12</v>
@@ -5556,28 +5556,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M46">
-        <v>0.11022396</v>
+        <v>0.11272905</v>
       </c>
       <c r="N46">
-        <v>0.4944427066666667</v>
+        <v>0.4919376166666667</v>
       </c>
       <c r="O46">
-        <v>0.0815830466</v>
+        <v>0.08116970675</v>
       </c>
       <c r="P46">
-        <v>0.4128596600666667</v>
+        <v>0.4107679099166667</v>
       </c>
       <c r="Q46">
-        <v>0.6598596600666666</v>
+        <v>0.6577679099166667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1137109855331196</v>
+        <v>0.114822708883251</v>
       </c>
       <c r="T46">
-        <v>1.323711510691401</v>
+        <v>1.345381068035047</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.485800606933978</v>
+        <v>5.36389392677989</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5602,22 +5602,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08393146488578808</v>
+        <v>0.08386755787302916</v>
       </c>
       <c r="C47">
-        <v>2.583137733423291</v>
+        <v>2.539660359308405</v>
       </c>
       <c r="D47">
-        <v>2.501637733423291</v>
+        <v>2.503460359308406</v>
       </c>
       <c r="E47">
-        <v>-1.1615</v>
+        <v>-1.1162</v>
       </c>
       <c r="F47">
-        <v>2.0385</v>
+        <v>2.083800000000001</v>
       </c>
       <c r="G47">
         <v>2.12</v>
@@ -5638,28 +5638,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M47">
-        <v>0.11272905</v>
+        <v>0.11523414</v>
       </c>
       <c r="N47">
-        <v>0.4919376166666667</v>
+        <v>0.4894325266666666</v>
       </c>
       <c r="O47">
-        <v>0.08116970675</v>
+        <v>0.0807563669</v>
       </c>
       <c r="P47">
-        <v>0.4107679099166667</v>
+        <v>0.4086761597666667</v>
       </c>
       <c r="Q47">
-        <v>0.6577679099166667</v>
+        <v>0.6556761597666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.114822708883251</v>
+        <v>0.1159756071722762</v>
       </c>
       <c r="T47">
-        <v>1.345381068035047</v>
+        <v>1.367853201576605</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.36389392677989</v>
+        <v>5.247287537067283</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5684,22 +5684,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08386755787302916</v>
+        <v>0.08380365086027027</v>
       </c>
       <c r="C48">
-        <v>2.539660359308405</v>
+        <v>2.496185642962173</v>
       </c>
       <c r="D48">
-        <v>2.503460359308406</v>
+        <v>2.505285642962174</v>
       </c>
       <c r="E48">
-        <v>-1.1162</v>
+        <v>-1.0709</v>
       </c>
       <c r="F48">
-        <v>2.083800000000001</v>
+        <v>2.129100000000001</v>
       </c>
       <c r="G48">
         <v>2.12</v>
@@ -5720,28 +5720,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M48">
-        <v>0.11523414</v>
+        <v>0.11773923</v>
       </c>
       <c r="N48">
-        <v>0.4894325266666666</v>
+        <v>0.4869274366666667</v>
       </c>
       <c r="O48">
-        <v>0.0807563669</v>
+        <v>0.08034302705</v>
       </c>
       <c r="P48">
-        <v>0.4086761597666667</v>
+        <v>0.4065844096166666</v>
       </c>
       <c r="Q48">
-        <v>0.6556761597666667</v>
+        <v>0.6535844096166666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1159756071722762</v>
+        <v>0.1171720110571137</v>
       </c>
       <c r="T48">
-        <v>1.367853201576605</v>
+        <v>1.391173340157468</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.247287537067283</v>
+        <v>5.135643121385001</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5766,22 +5766,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08380365086027027</v>
+        <v>0.08373974384751136</v>
       </c>
       <c r="C49">
-        <v>2.496185642962173</v>
+        <v>2.452713590202209</v>
       </c>
       <c r="D49">
-        <v>2.505285642962174</v>
+        <v>2.507113590202211</v>
       </c>
       <c r="E49">
-        <v>-1.0709</v>
+        <v>-1.0256</v>
       </c>
       <c r="F49">
-        <v>2.129100000000001</v>
+        <v>2.174400000000001</v>
       </c>
       <c r="G49">
         <v>2.12</v>
@@ -5802,28 +5802,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M49">
-        <v>0.11773923</v>
+        <v>0.12024432</v>
       </c>
       <c r="N49">
-        <v>0.4869274366666667</v>
+        <v>0.4844223466666666</v>
       </c>
       <c r="O49">
-        <v>0.08034302705</v>
+        <v>0.0799296872</v>
       </c>
       <c r="P49">
-        <v>0.4065844096166666</v>
+        <v>0.4044926594666666</v>
       </c>
       <c r="Q49">
-        <v>0.6535844096166666</v>
+        <v>0.6514926594666666</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1171720110571137</v>
+        <v>0.1184144304759834</v>
       </c>
       <c r="T49">
-        <v>1.391173340157468</v>
+        <v>1.415390407145286</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.135643121385001</v>
+        <v>5.028650556356146</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5848,22 +5848,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08373974384751136</v>
+        <v>0.08367583683475247</v>
       </c>
       <c r="C50">
-        <v>2.45271359020221</v>
+        <v>2.409244206863117</v>
       </c>
       <c r="D50">
-        <v>2.507113590202211</v>
+        <v>2.508944206863118</v>
       </c>
       <c r="E50">
-        <v>-1.0256</v>
+        <v>-0.9803000000000002</v>
       </c>
       <c r="F50">
-        <v>2.1744</v>
+        <v>2.2197</v>
       </c>
       <c r="G50">
         <v>2.12</v>
@@ -5884,28 +5884,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M50">
-        <v>0.12024432</v>
+        <v>0.12274941</v>
       </c>
       <c r="N50">
-        <v>0.4844223466666667</v>
+        <v>0.4819172566666666</v>
       </c>
       <c r="O50">
-        <v>0.0799296872</v>
+        <v>0.07951634735</v>
       </c>
       <c r="P50">
-        <v>0.4044926594666667</v>
+        <v>0.4024009093166666</v>
       </c>
       <c r="Q50">
-        <v>0.6514926594666667</v>
+        <v>0.6494009093166666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1184144304759834</v>
+        <v>0.1197055722250048</v>
       </c>
       <c r="T50">
-        <v>1.415390407145286</v>
+        <v>1.440557163034587</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.028650556356147</v>
+        <v>4.926025034797858</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5930,22 +5930,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08367583683475247</v>
+        <v>0.08361192982199356</v>
       </c>
       <c r="C51">
-        <v>2.409244206863117</v>
+        <v>2.365777498796556</v>
       </c>
       <c r="D51">
-        <v>2.508944206863118</v>
+        <v>2.510777498796556</v>
       </c>
       <c r="E51">
-        <v>-0.9803000000000002</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F51">
-        <v>2.2197</v>
+        <v>2.265000000000001</v>
       </c>
       <c r="G51">
         <v>2.12</v>
@@ -5966,28 +5966,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M51">
-        <v>0.12274941</v>
+        <v>0.1252545</v>
       </c>
       <c r="N51">
-        <v>0.4819172566666666</v>
+        <v>0.4794121666666666</v>
       </c>
       <c r="O51">
-        <v>0.07951634735</v>
+        <v>0.0791030075</v>
       </c>
       <c r="P51">
-        <v>0.4024009093166666</v>
+        <v>0.4003091591666667</v>
       </c>
       <c r="Q51">
-        <v>0.6494009093166666</v>
+        <v>0.6473091591666666</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1197055722250048</v>
+        <v>0.1210483596439871</v>
       </c>
       <c r="T51">
-        <v>1.440557163034587</v>
+        <v>1.466730589159461</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.926025034797858</v>
+        <v>4.8275045341019</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6012,22 +6012,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08361192982199356</v>
+        <v>0.08354802280923468</v>
       </c>
       <c r="C52">
-        <v>2.365777498796556</v>
+        <v>2.322313471871296</v>
       </c>
       <c r="D52">
-        <v>2.510777498796556</v>
+        <v>2.512613471871296</v>
       </c>
       <c r="E52">
-        <v>-0.9350000000000001</v>
+        <v>-0.8896999999999999</v>
       </c>
       <c r="F52">
-        <v>2.265000000000001</v>
+        <v>2.310300000000001</v>
       </c>
       <c r="G52">
         <v>2.12</v>
@@ -6048,28 +6048,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M52">
-        <v>0.1252545</v>
+        <v>0.12775959</v>
       </c>
       <c r="N52">
-        <v>0.4794121666666666</v>
+        <v>0.4769070766666667</v>
       </c>
       <c r="O52">
-        <v>0.0791030075</v>
+        <v>0.07868966765</v>
       </c>
       <c r="P52">
-        <v>0.4003091591666667</v>
+        <v>0.3982174090166666</v>
       </c>
       <c r="Q52">
-        <v>0.6473091591666666</v>
+        <v>0.6452174090166667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1210483596439871</v>
+        <v>0.1224459547127238</v>
       </c>
       <c r="T52">
-        <v>1.466730589159461</v>
+        <v>1.493972318391473</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.8275045341019</v>
+        <v>4.732847582452844</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6094,22 +6094,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08354802280923468</v>
+        <v>0.08348411579647577</v>
       </c>
       <c r="C53">
-        <v>2.322313471871296</v>
+        <v>2.278852131973292</v>
       </c>
       <c r="D53">
-        <v>2.512613471871296</v>
+        <v>2.514452131973293</v>
       </c>
       <c r="E53">
-        <v>-0.8896999999999999</v>
+        <v>-0.8443999999999998</v>
       </c>
       <c r="F53">
-        <v>2.310300000000001</v>
+        <v>2.355600000000001</v>
       </c>
       <c r="G53">
         <v>2.12</v>
@@ -6130,28 +6130,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M53">
-        <v>0.12775959</v>
+        <v>0.13026468</v>
       </c>
       <c r="N53">
-        <v>0.4769070766666667</v>
+        <v>0.4744019866666667</v>
       </c>
       <c r="O53">
-        <v>0.07868966765</v>
+        <v>0.0782763278</v>
       </c>
       <c r="P53">
-        <v>0.3982174090166666</v>
+        <v>0.3961256588666667</v>
       </c>
       <c r="Q53">
-        <v>0.6452174090166667</v>
+        <v>0.6431256588666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1224459547127238</v>
+        <v>0.1239017829093245</v>
       </c>
       <c r="T53">
-        <v>1.493972318391473</v>
+        <v>1.522349119674818</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.732847582452844</v>
+        <v>4.641831282790289</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6176,22 +6176,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08348411579647577</v>
+        <v>0.08342020878371686</v>
       </c>
       <c r="C54">
-        <v>2.278852131973292</v>
+        <v>2.235393485005738</v>
       </c>
       <c r="D54">
-        <v>2.514452131973293</v>
+        <v>2.516293485005739</v>
       </c>
       <c r="E54">
-        <v>-0.8443999999999998</v>
+        <v>-0.7990999999999997</v>
       </c>
       <c r="F54">
-        <v>2.355600000000001</v>
+        <v>2.400900000000001</v>
       </c>
       <c r="G54">
         <v>2.12</v>
@@ -6212,28 +6212,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M54">
-        <v>0.13026468</v>
+        <v>0.1327697700000001</v>
       </c>
       <c r="N54">
-        <v>0.4744019866666667</v>
+        <v>0.4718968966666666</v>
       </c>
       <c r="O54">
-        <v>0.0782763278</v>
+        <v>0.07786298794999999</v>
       </c>
       <c r="P54">
-        <v>0.3961256588666667</v>
+        <v>0.3940339087166667</v>
       </c>
       <c r="Q54">
-        <v>0.6431256588666667</v>
+        <v>0.6410339087166667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1239017829093245</v>
+        <v>0.1254195612419508</v>
       </c>
       <c r="T54">
-        <v>1.522349119674818</v>
+        <v>1.551933444417029</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.641831282790289</v>
+        <v>4.55424956047349</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6258,22 +6258,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08342020878371686</v>
+        <v>0.08448355177095797</v>
       </c>
       <c r="C55">
-        <v>2.235393485005738</v>
+        <v>2.159802037775876</v>
       </c>
       <c r="D55">
-        <v>2.516293485005739</v>
+        <v>2.486002037775877</v>
       </c>
       <c r="E55">
-        <v>-0.7990999999999997</v>
+        <v>-0.7538</v>
       </c>
       <c r="F55">
-        <v>2.400900000000001</v>
+        <v>2.446200000000001</v>
       </c>
       <c r="G55">
         <v>2.12</v>
@@ -6294,45 +6294,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M55">
-        <v>0.1327697700000001</v>
+        <v>0.14139036</v>
       </c>
       <c r="N55">
-        <v>0.4718968966666666</v>
+        <v>0.4632763066666666</v>
       </c>
       <c r="O55">
-        <v>0.07786298794999999</v>
+        <v>0.0764405906</v>
       </c>
       <c r="P55">
-        <v>0.3940339087166667</v>
+        <v>0.3868357160666667</v>
       </c>
       <c r="Q55">
-        <v>0.6410339087166667</v>
+        <v>0.6338357160666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1254195612419508</v>
+        <v>0.1270033299368651</v>
       </c>
       <c r="T55">
-        <v>1.551933444417029</v>
+        <v>1.582804044148031</v>
       </c>
       <c r="U55">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.165</v>
       </c>
       <c r="W55">
-        <v>0.0461755</v>
+        <v>0.048263</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.55424956047349</v>
+        <v>4.276576328588925</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6340,22 +6340,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08448355177095797</v>
+        <v>0.08444051975819908</v>
       </c>
       <c r="C56">
-        <v>2.159802037775876</v>
+        <v>2.115713723870868</v>
       </c>
       <c r="D56">
-        <v>2.486002037775877</v>
+        <v>2.487213723870868</v>
       </c>
       <c r="E56">
-        <v>-0.7538</v>
+        <v>-0.7084999999999999</v>
       </c>
       <c r="F56">
-        <v>2.446200000000001</v>
+        <v>2.491500000000001</v>
       </c>
       <c r="G56">
         <v>2.12</v>
@@ -6376,28 +6376,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M56">
-        <v>0.14139036</v>
+        <v>0.1440087</v>
       </c>
       <c r="N56">
-        <v>0.4632763066666666</v>
+        <v>0.4606579666666666</v>
       </c>
       <c r="O56">
-        <v>0.0764405906</v>
+        <v>0.0760085645</v>
       </c>
       <c r="P56">
-        <v>0.3868357160666667</v>
+        <v>0.3846494021666667</v>
       </c>
       <c r="Q56">
-        <v>0.6338357160666667</v>
+        <v>0.6316494021666667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1270033299368651</v>
+        <v>0.1286574883515535</v>
       </c>
       <c r="T56">
-        <v>1.582804044148031</v>
+        <v>1.615046670533746</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.276576328588925</v>
+        <v>4.198820395341855</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6422,22 +6422,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08444051975819908</v>
+        <v>0.08439748774544018</v>
       </c>
       <c r="C57">
-        <v>2.115713723870868</v>
+        <v>2.07162659170193</v>
       </c>
       <c r="D57">
-        <v>2.487213723870868</v>
+        <v>2.488426591701931</v>
       </c>
       <c r="E57">
-        <v>-0.7084999999999999</v>
+        <v>-0.6631999999999998</v>
       </c>
       <c r="F57">
-        <v>2.491500000000001</v>
+        <v>2.536800000000001</v>
       </c>
       <c r="G57">
         <v>2.12</v>
@@ -6458,28 +6458,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M57">
-        <v>0.1440087</v>
+        <v>0.1466270400000001</v>
       </c>
       <c r="N57">
-        <v>0.4606579666666666</v>
+        <v>0.4580396266666666</v>
       </c>
       <c r="O57">
-        <v>0.0760085645</v>
+        <v>0.0755765384</v>
       </c>
       <c r="P57">
-        <v>0.3846494021666667</v>
+        <v>0.3824630882666666</v>
       </c>
       <c r="Q57">
-        <v>0.6316494021666667</v>
+        <v>0.6294630882666666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1286574883515535</v>
+        <v>0.1303868357850913</v>
       </c>
       <c r="T57">
-        <v>1.615046670533746</v>
+        <v>1.648754870846082</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.198820395341855</v>
+        <v>4.123841459710749</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6504,22 +6504,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08439748774544018</v>
+        <v>0.08435445573268127</v>
       </c>
       <c r="C58">
-        <v>2.07162659170193</v>
+        <v>2.027540642998696</v>
       </c>
       <c r="D58">
-        <v>2.488426591701931</v>
+        <v>2.489640642998696</v>
       </c>
       <c r="E58">
-        <v>-0.6631999999999998</v>
+        <v>-0.6178999999999997</v>
       </c>
       <c r="F58">
-        <v>2.536800000000001</v>
+        <v>2.582100000000001</v>
       </c>
       <c r="G58">
         <v>2.12</v>
@@ -6540,28 +6540,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M58">
-        <v>0.1466270400000001</v>
+        <v>0.1492453800000001</v>
       </c>
       <c r="N58">
-        <v>0.4580396266666666</v>
+        <v>0.4554212866666666</v>
       </c>
       <c r="O58">
-        <v>0.0755765384</v>
+        <v>0.07514451229999999</v>
       </c>
       <c r="P58">
-        <v>0.3824630882666666</v>
+        <v>0.3802767743666666</v>
       </c>
       <c r="Q58">
-        <v>0.6294630882666666</v>
+        <v>0.6272767743666666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1303868357850913</v>
+        <v>0.1321966179829797</v>
       </c>
       <c r="T58">
-        <v>1.648754870846082</v>
+        <v>1.684030894428761</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.123841459710749</v>
+        <v>4.051493363926349</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6586,22 +6586,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08435445573268127</v>
+        <v>0.08600647371992237</v>
       </c>
       <c r="C59">
-        <v>2.027540642998696</v>
+        <v>1.936467268572475</v>
       </c>
       <c r="D59">
-        <v>2.489640642998696</v>
+        <v>2.443867268572477</v>
       </c>
       <c r="E59">
-        <v>-0.6178999999999997</v>
+        <v>-0.5725999999999996</v>
       </c>
       <c r="F59">
-        <v>2.582100000000001</v>
+        <v>2.627400000000001</v>
       </c>
       <c r="G59">
         <v>2.12</v>
@@ -6622,45 +6622,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M59">
-        <v>0.1492453800000001</v>
+        <v>0.1610596200000001</v>
       </c>
       <c r="N59">
-        <v>0.4554212866666666</v>
+        <v>0.4436070466666666</v>
       </c>
       <c r="O59">
-        <v>0.07514451229999999</v>
+        <v>0.0731951627</v>
       </c>
       <c r="P59">
-        <v>0.3802767743666666</v>
+        <v>0.3704118839666666</v>
       </c>
       <c r="Q59">
-        <v>0.6272767743666666</v>
+        <v>0.6174118839666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1321966179829797</v>
+        <v>0.1340925802855295</v>
       </c>
       <c r="T59">
-        <v>1.684030894428761</v>
+        <v>1.720986728658234</v>
       </c>
       <c r="U59">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V59">
         <v>0.165</v>
       </c>
       <c r="W59">
-        <v>0.048263</v>
+        <v>0.05118549999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.051493363926349</v>
+        <v>3.754303323618089</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6668,22 +6668,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08600647371992239</v>
+        <v>0.08599266670716346</v>
       </c>
       <c r="C60">
-        <v>1.936467268572476</v>
+        <v>1.891542851266677</v>
       </c>
       <c r="D60">
-        <v>2.443867268572476</v>
+        <v>2.444242851266678</v>
       </c>
       <c r="E60">
-        <v>-0.5726</v>
+        <v>-0.5272999999999999</v>
       </c>
       <c r="F60">
-        <v>2.627400000000001</v>
+        <v>2.672700000000001</v>
       </c>
       <c r="G60">
         <v>2.12</v>
@@ -6704,28 +6704,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M60">
-        <v>0.16105962</v>
+        <v>0.16383651</v>
       </c>
       <c r="N60">
-        <v>0.4436070466666666</v>
+        <v>0.4408301566666666</v>
       </c>
       <c r="O60">
-        <v>0.0731951627</v>
+        <v>0.07273697585</v>
       </c>
       <c r="P60">
-        <v>0.3704118839666666</v>
+        <v>0.3680931808166666</v>
       </c>
       <c r="Q60">
-        <v>0.6174118839666667</v>
+        <v>0.6150931808166666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1340925802855295</v>
+        <v>0.1360810285540572</v>
       </c>
       <c r="T60">
-        <v>1.720986728658234</v>
+        <v>1.759745286508656</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.754303323618089</v>
+        <v>3.690671063895749</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6750,22 +6750,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08599266670716346</v>
+        <v>0.08597885969440457</v>
       </c>
       <c r="C61">
-        <v>1.891542851266677</v>
+        <v>1.846618549420539</v>
       </c>
       <c r="D61">
-        <v>2.444242851266678</v>
+        <v>2.444618549420539</v>
       </c>
       <c r="E61">
-        <v>-0.5272999999999999</v>
+        <v>-0.4820000000000002</v>
       </c>
       <c r="F61">
-        <v>2.672700000000001</v>
+        <v>2.718</v>
       </c>
       <c r="G61">
         <v>2.12</v>
@@ -6786,28 +6786,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M61">
-        <v>0.16383651</v>
+        <v>0.1666134</v>
       </c>
       <c r="N61">
-        <v>0.4408301566666666</v>
+        <v>0.4380532666666667</v>
       </c>
       <c r="O61">
-        <v>0.07273697585</v>
+        <v>0.072278789</v>
       </c>
       <c r="P61">
-        <v>0.3680931808166666</v>
+        <v>0.3657744776666667</v>
       </c>
       <c r="Q61">
-        <v>0.6150931808166666</v>
+        <v>0.6127744776666666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1360810285540572</v>
+        <v>0.1381688992360114</v>
       </c>
       <c r="T61">
-        <v>1.759745286508656</v>
+        <v>1.8004417722516</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6824,7 +6824,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.690671063895749</v>
+        <v>3.629159879497487</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6832,22 +6832,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08597885969440457</v>
+        <v>0.08596505268164567</v>
       </c>
       <c r="C62">
-        <v>1.846618549420539</v>
+        <v>1.801694363087309</v>
       </c>
       <c r="D62">
-        <v>2.444618549420539</v>
+        <v>2.44499436308731</v>
       </c>
       <c r="E62">
-        <v>-0.4820000000000002</v>
+        <v>-0.4367000000000001</v>
       </c>
       <c r="F62">
-        <v>2.718</v>
+        <v>2.763300000000001</v>
       </c>
       <c r="G62">
         <v>2.12</v>
@@ -6868,28 +6868,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M62">
-        <v>0.1666134</v>
+        <v>0.16939029</v>
       </c>
       <c r="N62">
-        <v>0.4380532666666667</v>
+        <v>0.4352763766666666</v>
       </c>
       <c r="O62">
-        <v>0.072278789</v>
+        <v>0.07182060215</v>
       </c>
       <c r="P62">
-        <v>0.3657744776666667</v>
+        <v>0.3634557745166667</v>
       </c>
       <c r="Q62">
-        <v>0.6127744776666666</v>
+        <v>0.6104557745166667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1381688992360114</v>
+        <v>0.1403638402093479</v>
       </c>
       <c r="T62">
-        <v>1.8004417722516</v>
+        <v>1.843225257263413</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.629159879497487</v>
+        <v>3.56966545524343</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6914,22 +6914,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08596505268164567</v>
+        <v>0.08595124566888677</v>
       </c>
       <c r="C63">
-        <v>1.801694363087309</v>
+        <v>1.756770292320272</v>
       </c>
       <c r="D63">
-        <v>2.44499436308731</v>
+        <v>2.445370292320273</v>
       </c>
       <c r="E63">
-        <v>-0.4367000000000001</v>
+        <v>-0.3914</v>
       </c>
       <c r="F63">
-        <v>2.763300000000001</v>
+        <v>2.808600000000001</v>
       </c>
       <c r="G63">
         <v>2.12</v>
@@ -6950,28 +6950,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M63">
-        <v>0.16939029</v>
+        <v>0.17216718</v>
       </c>
       <c r="N63">
-        <v>0.4352763766666666</v>
+        <v>0.4324994866666667</v>
       </c>
       <c r="O63">
-        <v>0.07182060215</v>
+        <v>0.0713624153</v>
       </c>
       <c r="P63">
-        <v>0.3634557745166667</v>
+        <v>0.3611370713666667</v>
       </c>
       <c r="Q63">
-        <v>0.6104557745166667</v>
+        <v>0.6081370713666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1403638402093479</v>
+        <v>0.1426743043918073</v>
       </c>
       <c r="T63">
-        <v>1.843225257263413</v>
+        <v>1.888260504644268</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.56966545524343</v>
+        <v>3.51209020596531</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6996,22 +6996,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08595124566888677</v>
+        <v>0.08741037865612789</v>
       </c>
       <c r="C64">
-        <v>1.756770292320272</v>
+        <v>1.672371086271774</v>
       </c>
       <c r="D64">
-        <v>2.445370292320273</v>
+        <v>2.406271086271774</v>
       </c>
       <c r="E64">
-        <v>-0.3914</v>
+        <v>-0.3460999999999999</v>
       </c>
       <c r="F64">
-        <v>2.808600000000001</v>
+        <v>2.853900000000001</v>
       </c>
       <c r="G64">
         <v>2.12</v>
@@ -7032,45 +7032,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M64">
-        <v>0.17216718</v>
+        <v>0.1829349900000001</v>
       </c>
       <c r="N64">
-        <v>0.4324994866666667</v>
+        <v>0.4217316766666666</v>
       </c>
       <c r="O64">
-        <v>0.0713624153</v>
+        <v>0.06958572665</v>
       </c>
       <c r="P64">
-        <v>0.3611370713666667</v>
+        <v>0.3521459500166666</v>
       </c>
       <c r="Q64">
-        <v>0.6081370713666667</v>
+        <v>0.5991459500166666</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1426743043918073</v>
+        <v>0.1451096585300753</v>
       </c>
       <c r="T64">
-        <v>1.888260504644268</v>
+        <v>1.935730089721386</v>
       </c>
       <c r="U64">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V64">
         <v>0.165</v>
       </c>
       <c r="W64">
-        <v>0.05118549999999999</v>
+        <v>0.0535235</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.51209020596531</v>
+        <v>3.305363652227857</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7078,22 +7078,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08741037865612789</v>
+        <v>0.08741995164336899</v>
       </c>
       <c r="C65">
-        <v>1.672371086271774</v>
+        <v>1.626818694664962</v>
       </c>
       <c r="D65">
-        <v>2.406271086271774</v>
+        <v>2.406018694664963</v>
       </c>
       <c r="E65">
-        <v>-0.3460999999999999</v>
+        <v>-0.3007999999999997</v>
       </c>
       <c r="F65">
-        <v>2.853900000000001</v>
+        <v>2.899200000000001</v>
       </c>
       <c r="G65">
         <v>2.12</v>
@@ -7114,28 +7114,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M65">
-        <v>0.1829349900000001</v>
+        <v>0.1858387200000001</v>
       </c>
       <c r="N65">
-        <v>0.4217316766666666</v>
+        <v>0.4188279466666666</v>
       </c>
       <c r="O65">
-        <v>0.06958572665</v>
+        <v>0.0691066112</v>
       </c>
       <c r="P65">
-        <v>0.3521459500166666</v>
+        <v>0.3497213354666666</v>
       </c>
       <c r="Q65">
-        <v>0.5991459500166666</v>
+        <v>0.5967213354666666</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1451096585300753</v>
+        <v>0.1476803101204694</v>
       </c>
       <c r="T65">
-        <v>1.935730089721386</v>
+        <v>1.985836873969455</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.305363652227857</v>
+        <v>3.253717345161796</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7160,22 +7160,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08741995164336899</v>
+        <v>0.08742952463061009</v>
       </c>
       <c r="C66">
-        <v>1.626818694664962</v>
+        <v>1.581266355998855</v>
       </c>
       <c r="D66">
-        <v>2.406018694664963</v>
+        <v>2.405766355998856</v>
       </c>
       <c r="E66">
-        <v>-0.3007999999999997</v>
+        <v>-0.2554999999999996</v>
       </c>
       <c r="F66">
-        <v>2.899200000000001</v>
+        <v>2.944500000000001</v>
       </c>
       <c r="G66">
         <v>2.12</v>
@@ -7196,28 +7196,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M66">
-        <v>0.1858387200000001</v>
+        <v>0.1887424500000001</v>
       </c>
       <c r="N66">
-        <v>0.4188279466666666</v>
+        <v>0.4159242166666666</v>
       </c>
       <c r="O66">
-        <v>0.0691066112</v>
+        <v>0.06862749574999999</v>
       </c>
       <c r="P66">
-        <v>0.3497213354666666</v>
+        <v>0.3472967209166666</v>
       </c>
       <c r="Q66">
-        <v>0.5967213354666666</v>
+        <v>0.5942967209166665</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1476803101204694</v>
+        <v>0.1503978560874574</v>
       </c>
       <c r="T66">
-        <v>1.985836873969455</v>
+        <v>2.0388069030317</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.253717345161796</v>
+        <v>3.20366015523623</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7242,22 +7242,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08742952463061009</v>
+        <v>0.08743909761785118</v>
       </c>
       <c r="C67">
-        <v>1.581266355998855</v>
+        <v>1.535714070256796</v>
       </c>
       <c r="D67">
-        <v>2.405766355998856</v>
+        <v>2.405514070256797</v>
       </c>
       <c r="E67">
-        <v>-0.2554999999999996</v>
+        <v>-0.2101999999999999</v>
       </c>
       <c r="F67">
-        <v>2.944500000000001</v>
+        <v>2.989800000000001</v>
       </c>
       <c r="G67">
         <v>2.12</v>
@@ -7278,28 +7278,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M67">
-        <v>0.1887424500000001</v>
+        <v>0.1916461800000001</v>
       </c>
       <c r="N67">
-        <v>0.4159242166666666</v>
+        <v>0.4130204866666666</v>
       </c>
       <c r="O67">
-        <v>0.06862749574999999</v>
+        <v>0.06814838029999999</v>
       </c>
       <c r="P67">
-        <v>0.3472967209166666</v>
+        <v>0.3448721063666667</v>
       </c>
       <c r="Q67">
-        <v>0.5942967209166665</v>
+        <v>0.5918721063666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1503978560874574</v>
+        <v>0.1532752576995623</v>
       </c>
       <c r="T67">
-        <v>2.0388069030317</v>
+        <v>2.094892816156429</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -7316,7 +7316,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.20366015523623</v>
+        <v>3.155119849853864</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7324,22 +7324,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08743909761785118</v>
+        <v>0.08744867060509229</v>
       </c>
       <c r="C68">
-        <v>1.535714070256796</v>
+        <v>1.490161837422137</v>
       </c>
       <c r="D68">
-        <v>2.405514070256797</v>
+        <v>2.405261837422138</v>
       </c>
       <c r="E68">
-        <v>-0.2101999999999999</v>
+        <v>-0.1648999999999998</v>
       </c>
       <c r="F68">
-        <v>2.989800000000001</v>
+        <v>3.035100000000001</v>
       </c>
       <c r="G68">
         <v>2.12</v>
@@ -7360,28 +7360,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M68">
-        <v>0.1916461800000001</v>
+        <v>0.1945499100000001</v>
       </c>
       <c r="N68">
-        <v>0.4130204866666666</v>
+        <v>0.4101167566666666</v>
       </c>
       <c r="O68">
-        <v>0.06814838029999999</v>
+        <v>0.06766926484999999</v>
       </c>
       <c r="P68">
-        <v>0.3448721063666667</v>
+        <v>0.3424474918166666</v>
       </c>
       <c r="Q68">
-        <v>0.5918721063666667</v>
+        <v>0.5894474918166666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1532752576995623</v>
+        <v>0.1563270472881584</v>
       </c>
       <c r="T68">
-        <v>2.094892816156429</v>
+        <v>2.154377875531142</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.155119849853864</v>
+        <v>3.108028508811268</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7406,22 +7406,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08744867060509229</v>
+        <v>0.0874582435923334</v>
       </c>
       <c r="C69">
-        <v>1.490161837422137</v>
+        <v>1.444609657478237</v>
       </c>
       <c r="D69">
-        <v>2.405261837422138</v>
+        <v>2.405009657478238</v>
       </c>
       <c r="E69">
-        <v>-0.1648999999999998</v>
+        <v>-0.1195999999999997</v>
       </c>
       <c r="F69">
-        <v>3.035100000000001</v>
+        <v>3.080400000000001</v>
       </c>
       <c r="G69">
         <v>2.12</v>
@@ -7442,28 +7442,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M69">
-        <v>0.1945499100000001</v>
+        <v>0.1974536400000001</v>
       </c>
       <c r="N69">
-        <v>0.4101167566666666</v>
+        <v>0.4072130266666666</v>
       </c>
       <c r="O69">
-        <v>0.06766926484999999</v>
+        <v>0.0671901494</v>
       </c>
       <c r="P69">
-        <v>0.3424474918166666</v>
+        <v>0.3400228772666666</v>
       </c>
       <c r="Q69">
-        <v>0.5894474918166666</v>
+        <v>0.5870228772666666</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1563270472881584</v>
+        <v>0.1595695737260419</v>
       </c>
       <c r="T69">
-        <v>2.154377875531142</v>
+        <v>2.217580751116774</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.108028508811268</v>
+        <v>3.062322207211102</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7488,22 +7488,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0874582435923334</v>
+        <v>0.0874678165795745</v>
       </c>
       <c r="C70">
-        <v>1.444609657478237</v>
+        <v>1.399057530408461</v>
       </c>
       <c r="D70">
-        <v>2.405009657478238</v>
+        <v>2.404757530408462</v>
       </c>
       <c r="E70">
-        <v>-0.1195999999999997</v>
+        <v>-0.07429999999999959</v>
       </c>
       <c r="F70">
-        <v>3.080400000000001</v>
+        <v>3.125700000000001</v>
       </c>
       <c r="G70">
         <v>2.12</v>
@@ -7524,28 +7524,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M70">
-        <v>0.1974536400000001</v>
+        <v>0.2003573700000001</v>
       </c>
       <c r="N70">
-        <v>0.4072130266666666</v>
+        <v>0.4043092966666666</v>
       </c>
       <c r="O70">
-        <v>0.0671901494</v>
+        <v>0.06671103395</v>
       </c>
       <c r="P70">
-        <v>0.3400228772666666</v>
+        <v>0.3375982627166666</v>
       </c>
       <c r="Q70">
-        <v>0.5870228772666666</v>
+        <v>0.5845982627166666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1595695737260419</v>
+        <v>0.1630212954179823</v>
       </c>
       <c r="T70">
-        <v>2.217580751116774</v>
+        <v>2.284861231578899</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.062322207211102</v>
+        <v>3.017940725947173</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7570,22 +7570,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0874678165795745</v>
+        <v>0.09203648956681559</v>
       </c>
       <c r="C71">
-        <v>1.399057530408461</v>
+        <v>1.239176129183061</v>
       </c>
       <c r="D71">
-        <v>2.404757530408462</v>
+        <v>2.290176129183062</v>
       </c>
       <c r="E71">
-        <v>-0.07429999999999959</v>
+        <v>-0.02899999999999947</v>
       </c>
       <c r="F71">
-        <v>3.125700000000001</v>
+        <v>3.171000000000001</v>
       </c>
       <c r="G71">
         <v>2.12</v>
@@ -7606,45 +7606,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M71">
-        <v>0.2003573700000001</v>
+        <v>0.2279949000000001</v>
       </c>
       <c r="N71">
-        <v>0.4043092966666666</v>
+        <v>0.3766717666666666</v>
       </c>
       <c r="O71">
-        <v>0.06671103395</v>
+        <v>0.06215084149999999</v>
       </c>
       <c r="P71">
-        <v>0.3375982627166666</v>
+        <v>0.3145209251666666</v>
       </c>
       <c r="Q71">
-        <v>0.5845982627166666</v>
+        <v>0.5615209251666666</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1630212954179823</v>
+        <v>0.1667031318893853</v>
       </c>
       <c r="T71">
-        <v>2.284861231578899</v>
+        <v>2.356627077405165</v>
       </c>
       <c r="U71">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V71">
         <v>0.165</v>
       </c>
       <c r="W71">
-        <v>0.0535235</v>
+        <v>0.0600365</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.017940725947173</v>
+        <v>2.652106107051809</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7652,22 +7652,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09203648956681559</v>
+        <v>0.0921111925540567</v>
       </c>
       <c r="C72">
-        <v>1.239176129183061</v>
+        <v>1.1920932521547</v>
       </c>
       <c r="D72">
-        <v>2.290176129183062</v>
+        <v>2.288393252154701</v>
       </c>
       <c r="E72">
-        <v>-0.02899999999999947</v>
+        <v>0.01630000000000065</v>
       </c>
       <c r="F72">
-        <v>3.171000000000001</v>
+        <v>3.216300000000001</v>
       </c>
       <c r="G72">
         <v>2.12</v>
@@ -7688,28 +7688,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M72">
-        <v>0.2279949000000001</v>
+        <v>0.2312519700000001</v>
       </c>
       <c r="N72">
-        <v>0.3766717666666666</v>
+        <v>0.3734146966666666</v>
       </c>
       <c r="O72">
-        <v>0.06215084149999999</v>
+        <v>0.06161342495</v>
       </c>
       <c r="P72">
-        <v>0.3145209251666666</v>
+        <v>0.3118012717166666</v>
       </c>
       <c r="Q72">
-        <v>0.5615209251666666</v>
+        <v>0.5588012717166666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1667031318893853</v>
+        <v>0.1706388881174369</v>
       </c>
       <c r="T72">
-        <v>2.356627077405165</v>
+        <v>2.433342291909106</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.652106107051809</v>
+        <v>2.614752499910234</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7734,22 +7734,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0921111925540567</v>
+        <v>0.0921858955412978</v>
       </c>
       <c r="C73">
-        <v>1.1920932521547</v>
+        <v>1.145013148867485</v>
       </c>
       <c r="D73">
-        <v>2.288393252154701</v>
+        <v>2.286613148867485</v>
       </c>
       <c r="E73">
-        <v>0.0163000000000002</v>
+        <v>0.06159999999999988</v>
       </c>
       <c r="F73">
-        <v>3.216300000000001</v>
+        <v>3.2616</v>
       </c>
       <c r="G73">
         <v>2.12</v>
@@ -7770,28 +7770,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M73">
-        <v>0.2312519700000001</v>
+        <v>0.2345090400000001</v>
       </c>
       <c r="N73">
-        <v>0.3734146966666666</v>
+        <v>0.3701576266666666</v>
       </c>
       <c r="O73">
-        <v>0.06161342495</v>
+        <v>0.0610760084</v>
       </c>
       <c r="P73">
-        <v>0.3118012717166666</v>
+        <v>0.3090816182666666</v>
       </c>
       <c r="Q73">
-        <v>0.5588012717166666</v>
+        <v>0.5560816182666666</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1706388881174369</v>
+        <v>0.1748557697903493</v>
       </c>
       <c r="T73">
-        <v>2.433342291909105</v>
+        <v>2.515537164591898</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7808,7 +7808,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.614752499910234</v>
+        <v>2.578436492967037</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7816,22 +7816,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0921858955412978</v>
+        <v>0.09226059852853891</v>
       </c>
       <c r="C74">
-        <v>1.145013148867485</v>
+        <v>1.097935812853502</v>
       </c>
       <c r="D74">
-        <v>2.286613148867485</v>
+        <v>2.284835812853502</v>
       </c>
       <c r="E74">
-        <v>0.06159999999999988</v>
+        <v>0.1069</v>
       </c>
       <c r="F74">
-        <v>3.2616</v>
+        <v>3.306900000000001</v>
       </c>
       <c r="G74">
         <v>2.12</v>
@@ -7852,28 +7852,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M74">
-        <v>0.2345090400000001</v>
+        <v>0.2377661100000001</v>
       </c>
       <c r="N74">
-        <v>0.3701576266666666</v>
+        <v>0.3669005566666667</v>
       </c>
       <c r="O74">
-        <v>0.0610760084</v>
+        <v>0.06053859185</v>
       </c>
       <c r="P74">
-        <v>0.3090816182666666</v>
+        <v>0.3063619648166667</v>
       </c>
       <c r="Q74">
-        <v>0.5560816182666666</v>
+        <v>0.5533619648166667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1748557697903493</v>
+        <v>0.1793850130686626</v>
       </c>
       <c r="T74">
-        <v>2.515537164591898</v>
+        <v>2.603820546362305</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.578436492967037</v>
+        <v>2.543115445118174</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7898,22 +7898,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09226059852853891</v>
+        <v>0.09233530151578</v>
       </c>
       <c r="C75">
-        <v>1.097935812853502</v>
+        <v>1.050861237664936</v>
       </c>
       <c r="D75">
-        <v>2.284835812853502</v>
+        <v>2.283061237664937</v>
       </c>
       <c r="E75">
-        <v>0.1069</v>
+        <v>0.1522000000000001</v>
       </c>
       <c r="F75">
-        <v>3.306900000000001</v>
+        <v>3.352200000000001</v>
       </c>
       <c r="G75">
         <v>2.12</v>
@@ -7934,28 +7934,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M75">
-        <v>0.2377661100000001</v>
+        <v>0.2410231800000001</v>
       </c>
       <c r="N75">
-        <v>0.3669005566666667</v>
+        <v>0.3636434866666666</v>
       </c>
       <c r="O75">
-        <v>0.06053859185</v>
+        <v>0.06000117529999999</v>
       </c>
       <c r="P75">
-        <v>0.3063619648166667</v>
+        <v>0.3036423113666666</v>
       </c>
       <c r="Q75">
-        <v>0.5533619648166667</v>
+        <v>0.5506423113666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1793850130686626</v>
+        <v>0.1842626596760769</v>
       </c>
       <c r="T75">
-        <v>2.603820546362305</v>
+        <v>2.698894957499666</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7972,7 +7972,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.543115445118174</v>
+        <v>2.508749020184144</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7980,22 +7980,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09233530151578</v>
+        <v>0.09485237950302111</v>
       </c>
       <c r="C76">
-        <v>1.050861237664936</v>
+        <v>0.9473379801143205</v>
       </c>
       <c r="D76">
-        <v>2.283061237664937</v>
+        <v>2.224837980114321</v>
       </c>
       <c r="E76">
-        <v>0.1522000000000001</v>
+        <v>0.1975000000000002</v>
       </c>
       <c r="F76">
-        <v>3.352200000000001</v>
+        <v>3.397500000000001</v>
       </c>
       <c r="G76">
         <v>2.12</v>
@@ -8016,45 +8016,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M76">
-        <v>0.2410231800000001</v>
+        <v>0.2575305000000001</v>
       </c>
       <c r="N76">
-        <v>0.3636434866666666</v>
+        <v>0.3471361666666666</v>
       </c>
       <c r="O76">
-        <v>0.06000117529999999</v>
+        <v>0.05727746749999999</v>
       </c>
       <c r="P76">
-        <v>0.3036423113666666</v>
+        <v>0.2898586991666666</v>
       </c>
       <c r="Q76">
-        <v>0.5506423113666666</v>
+        <v>0.5368586991666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1842626596760769</v>
+        <v>0.1895305180120844</v>
       </c>
       <c r="T76">
-        <v>2.698894957499666</v>
+        <v>2.801575321528017</v>
       </c>
       <c r="U76">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V76">
         <v>0.165</v>
       </c>
       <c r="W76">
-        <v>0.0600365</v>
+        <v>0.063293</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.508749020184144</v>
+        <v>2.347941958978321</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8062,22 +8062,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09485237950302111</v>
+        <v>0.0949596474902622</v>
       </c>
       <c r="C77">
-        <v>0.9473379801143205</v>
+        <v>0.8996226357882797</v>
       </c>
       <c r="D77">
-        <v>2.224837980114321</v>
+        <v>2.222422635788281</v>
       </c>
       <c r="E77">
-        <v>0.1975000000000002</v>
+        <v>0.2428000000000003</v>
       </c>
       <c r="F77">
-        <v>3.397500000000001</v>
+        <v>3.442800000000001</v>
       </c>
       <c r="G77">
         <v>2.12</v>
@@ -8098,28 +8098,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M77">
-        <v>0.2575305000000001</v>
+        <v>0.2609642400000001</v>
       </c>
       <c r="N77">
-        <v>0.3471361666666666</v>
+        <v>0.3437024266666666</v>
       </c>
       <c r="O77">
-        <v>0.05727746749999999</v>
+        <v>0.05671090039999999</v>
       </c>
       <c r="P77">
-        <v>0.2898586991666666</v>
+        <v>0.2869915262666666</v>
       </c>
       <c r="Q77">
-        <v>0.5368586991666666</v>
+        <v>0.5339915262666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1895305180120844</v>
+        <v>0.1952373645427592</v>
       </c>
       <c r="T77">
-        <v>2.801575321528017</v>
+        <v>2.912812382558731</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.347941958978321</v>
+        <v>2.317047985833869</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8144,22 +8144,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0949596474902622</v>
+        <v>0.09506691547750332</v>
       </c>
       <c r="C78">
-        <v>0.8996226357882797</v>
+        <v>0.851912530101373</v>
       </c>
       <c r="D78">
-        <v>2.222422635788281</v>
+        <v>2.220012530101374</v>
       </c>
       <c r="E78">
-        <v>0.2428000000000003</v>
+        <v>0.2881000000000005</v>
       </c>
       <c r="F78">
-        <v>3.442800000000001</v>
+        <v>3.488100000000001</v>
       </c>
       <c r="G78">
         <v>2.12</v>
@@ -8180,28 +8180,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M78">
-        <v>0.2609642400000001</v>
+        <v>0.2643979800000001</v>
       </c>
       <c r="N78">
-        <v>0.3437024266666666</v>
+        <v>0.3402686866666666</v>
       </c>
       <c r="O78">
-        <v>0.05671090039999999</v>
+        <v>0.05614433329999999</v>
       </c>
       <c r="P78">
-        <v>0.2869915262666666</v>
+        <v>0.2841243533666666</v>
       </c>
       <c r="Q78">
-        <v>0.5339915262666666</v>
+        <v>0.5311243533666665</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1952373645427592</v>
+        <v>0.2014404585978405</v>
       </c>
       <c r="T78">
-        <v>2.912812382558731</v>
+        <v>3.033722231505157</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.317047985833869</v>
+        <v>2.286956453550313</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8226,22 +8226,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09506691547750332</v>
+        <v>0.09517418346474441</v>
       </c>
       <c r="C79">
-        <v>0.851912530101373</v>
+        <v>0.8042076460289396</v>
       </c>
       <c r="D79">
-        <v>2.220012530101374</v>
+        <v>2.217607646028941</v>
       </c>
       <c r="E79">
-        <v>0.2881000000000005</v>
+        <v>0.3334000000000006</v>
       </c>
       <c r="F79">
-        <v>3.488100000000001</v>
+        <v>3.533400000000001</v>
       </c>
       <c r="G79">
         <v>2.12</v>
@@ -8262,28 +8262,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M79">
-        <v>0.2643979800000001</v>
+        <v>0.2678317200000001</v>
       </c>
       <c r="N79">
-        <v>0.3402686866666666</v>
+        <v>0.3368349466666666</v>
       </c>
       <c r="O79">
-        <v>0.05614433329999999</v>
+        <v>0.05557776619999999</v>
       </c>
       <c r="P79">
-        <v>0.2841243533666666</v>
+        <v>0.2812571804666666</v>
       </c>
       <c r="Q79">
-        <v>0.5311243533666665</v>
+        <v>0.5282571804666666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2014404585978405</v>
+        <v>0.2082074702942928</v>
       </c>
       <c r="T79">
-        <v>3.033722231505157</v>
+        <v>3.16562388490126</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.286956453550313</v>
+        <v>2.257636499017616</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8308,22 +8308,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09517418346474441</v>
+        <v>0.09528145145198552</v>
       </c>
       <c r="C80">
-        <v>0.8042076460289396</v>
+        <v>0.7565079666200085</v>
       </c>
       <c r="D80">
-        <v>2.217607646028941</v>
+        <v>2.21520796662001</v>
       </c>
       <c r="E80">
-        <v>0.3334000000000006</v>
+        <v>0.3787000000000003</v>
       </c>
       <c r="F80">
-        <v>3.533400000000001</v>
+        <v>3.578700000000001</v>
       </c>
       <c r="G80">
         <v>2.12</v>
@@ -8344,28 +8344,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M80">
-        <v>0.2678317200000001</v>
+        <v>0.2712654600000001</v>
       </c>
       <c r="N80">
-        <v>0.3368349466666666</v>
+        <v>0.3334012066666666</v>
       </c>
       <c r="O80">
-        <v>0.05557776619999999</v>
+        <v>0.05501119909999999</v>
       </c>
       <c r="P80">
-        <v>0.2812571804666666</v>
+        <v>0.2783900075666667</v>
       </c>
       <c r="Q80">
-        <v>0.5282571804666666</v>
+        <v>0.5253900075666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2082074702942928</v>
+        <v>0.2156189592951691</v>
       </c>
       <c r="T80">
-        <v>3.16562388490126</v>
+        <v>3.310087600525563</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.257636499017616</v>
+        <v>2.229058821814862</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8390,22 +8390,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09528145145198552</v>
+        <v>0.09538871943922661</v>
       </c>
       <c r="C81">
-        <v>0.7565079666200085</v>
+        <v>0.7088134749969028</v>
       </c>
       <c r="D81">
-        <v>2.21520796662001</v>
+        <v>2.212813474996903</v>
       </c>
       <c r="E81">
-        <v>0.3787000000000003</v>
+        <v>0.4240000000000004</v>
       </c>
       <c r="F81">
-        <v>3.578700000000001</v>
+        <v>3.624000000000001</v>
       </c>
       <c r="G81">
         <v>2.12</v>
@@ -8426,28 +8426,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M81">
-        <v>0.2712654600000001</v>
+        <v>0.2746992000000001</v>
       </c>
       <c r="N81">
-        <v>0.3334012066666666</v>
+        <v>0.3299674666666666</v>
       </c>
       <c r="O81">
-        <v>0.05501119909999999</v>
+        <v>0.05444463199999999</v>
       </c>
       <c r="P81">
-        <v>0.2783900075666667</v>
+        <v>0.2755228346666666</v>
       </c>
       <c r="Q81">
-        <v>0.5253900075666667</v>
+        <v>0.5225228346666666</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2156189592951691</v>
+        <v>0.2237715971961331</v>
       </c>
       <c r="T81">
-        <v>3.310087600525563</v>
+        <v>3.468997687712296</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.229058821814862</v>
+        <v>2.201195586542176</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8472,22 +8472,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09538871943922661</v>
+        <v>0.09549598742646773</v>
       </c>
       <c r="C82">
-        <v>0.7088134749969028</v>
+        <v>0.6611241543548361</v>
       </c>
       <c r="D82">
-        <v>2.212813474996903</v>
+        <v>2.210424154354837</v>
       </c>
       <c r="E82">
-        <v>0.4240000000000004</v>
+        <v>0.4693000000000005</v>
       </c>
       <c r="F82">
-        <v>3.624000000000001</v>
+        <v>3.669300000000001</v>
       </c>
       <c r="G82">
         <v>2.12</v>
@@ -8508,28 +8508,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M82">
-        <v>0.2746992000000001</v>
+        <v>0.2781329400000001</v>
       </c>
       <c r="N82">
-        <v>0.3299674666666666</v>
+        <v>0.3265337266666666</v>
       </c>
       <c r="O82">
-        <v>0.05444463199999999</v>
+        <v>0.05387806489999999</v>
       </c>
       <c r="P82">
-        <v>0.2755228346666666</v>
+        <v>0.2726556617666666</v>
       </c>
       <c r="Q82">
-        <v>0.5225228346666666</v>
+        <v>0.5196556617666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2237715971961331</v>
+        <v>0.2327824075077249</v>
       </c>
       <c r="T82">
-        <v>3.468997687712296</v>
+        <v>3.644635152497633</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8546,7 +8546,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.201195586542176</v>
+        <v>2.174020332387334</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8554,22 +8554,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09549598742646773</v>
+        <v>0.09560325541370882</v>
       </c>
       <c r="C83">
-        <v>0.6611241543548361</v>
+        <v>0.6134399879615287</v>
       </c>
       <c r="D83">
-        <v>2.210424154354837</v>
+        <v>2.20803998796153</v>
       </c>
       <c r="E83">
-        <v>0.4693000000000005</v>
+        <v>0.5146000000000006</v>
       </c>
       <c r="F83">
-        <v>3.669300000000001</v>
+        <v>3.714600000000001</v>
       </c>
       <c r="G83">
         <v>2.12</v>
@@ -8590,28 +8590,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M83">
-        <v>0.2781329400000001</v>
+        <v>0.2815666800000001</v>
       </c>
       <c r="N83">
-        <v>0.3265337266666666</v>
+        <v>0.3230999866666666</v>
       </c>
       <c r="O83">
-        <v>0.05387806489999999</v>
+        <v>0.05331149779999998</v>
       </c>
       <c r="P83">
-        <v>0.2726556617666666</v>
+        <v>0.2697884888666666</v>
       </c>
       <c r="Q83">
-        <v>0.5196556617666666</v>
+        <v>0.5167884888666665</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2327824075077249</v>
+        <v>0.242794418965049</v>
       </c>
       <c r="T83">
-        <v>3.644635152497633</v>
+        <v>3.839787891148006</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.174020332387334</v>
+        <v>2.147507889309439</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8636,22 +8636,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09560325541370882</v>
+        <v>0.0957105234009499</v>
       </c>
       <c r="C84">
-        <v>0.6134399879615287</v>
+        <v>0.5657609591568122</v>
       </c>
       <c r="D84">
-        <v>2.20803998796153</v>
+        <v>2.205660959156813</v>
       </c>
       <c r="E84">
-        <v>0.5146000000000006</v>
+        <v>0.5599000000000007</v>
       </c>
       <c r="F84">
-        <v>3.714600000000001</v>
+        <v>3.759900000000001</v>
       </c>
       <c r="G84">
         <v>2.12</v>
@@ -8672,28 +8672,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M84">
-        <v>0.2815666800000001</v>
+        <v>0.2850004200000001</v>
       </c>
       <c r="N84">
-        <v>0.3230999866666666</v>
+        <v>0.3196662466666665</v>
       </c>
       <c r="O84">
-        <v>0.05331149779999998</v>
+        <v>0.05274493069999998</v>
       </c>
       <c r="P84">
-        <v>0.2697884888666666</v>
+        <v>0.2669213159666666</v>
       </c>
       <c r="Q84">
-        <v>0.5167884888666665</v>
+        <v>0.5139213159666666</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.242794418965049</v>
+        <v>0.2539843141232348</v>
       </c>
       <c r="T84">
-        <v>3.839787891148006</v>
+        <v>4.057899775521953</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.147507889309439</v>
+        <v>2.121634300281615</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8718,22 +8718,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0957105234009499</v>
+        <v>0.09581779138819102</v>
       </c>
       <c r="C85">
-        <v>0.5657609591568122</v>
+        <v>0.5180870513522406</v>
       </c>
       <c r="D85">
-        <v>2.205660959156813</v>
+        <v>2.203287051352242</v>
       </c>
       <c r="E85">
-        <v>0.5599000000000007</v>
+        <v>0.6052000000000008</v>
       </c>
       <c r="F85">
-        <v>3.759900000000001</v>
+        <v>3.805200000000001</v>
       </c>
       <c r="G85">
         <v>2.12</v>
@@ -8754,28 +8754,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M85">
-        <v>0.2850004200000001</v>
+        <v>0.2884341600000002</v>
       </c>
       <c r="N85">
-        <v>0.3196662466666665</v>
+        <v>0.3162325066666665</v>
       </c>
       <c r="O85">
-        <v>0.05274493069999998</v>
+        <v>0.05217836359999998</v>
       </c>
       <c r="P85">
-        <v>0.2669213159666666</v>
+        <v>0.2640541430666665</v>
       </c>
       <c r="Q85">
-        <v>0.5139213159666666</v>
+        <v>0.5110541430666665</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2539843141232348</v>
+        <v>0.2665729461761939</v>
       </c>
       <c r="T85">
-        <v>4.057899775521953</v>
+        <v>4.303275645442644</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.121634300281615</v>
+        <v>2.096376749087786</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8800,22 +8800,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09581779138819101</v>
+        <v>0.09592505937543211</v>
       </c>
       <c r="C86">
-        <v>0.5180870513522411</v>
+        <v>0.4704182480307106</v>
       </c>
       <c r="D86">
-        <v>2.203287051352242</v>
+        <v>2.200918248030712</v>
       </c>
       <c r="E86">
-        <v>0.6052000000000004</v>
+        <v>0.6505000000000001</v>
       </c>
       <c r="F86">
-        <v>3.805200000000001</v>
+        <v>3.850500000000001</v>
       </c>
       <c r="G86">
         <v>2.12</v>
@@ -8836,28 +8836,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M86">
-        <v>0.2884341600000001</v>
+        <v>0.2918679000000001</v>
       </c>
       <c r="N86">
-        <v>0.3162325066666666</v>
+        <v>0.3127987666666666</v>
       </c>
       <c r="O86">
-        <v>0.05217836359999999</v>
+        <v>0.05161179649999999</v>
       </c>
       <c r="P86">
-        <v>0.2640541430666666</v>
+        <v>0.2611869701666666</v>
       </c>
       <c r="Q86">
-        <v>0.5110541430666666</v>
+        <v>0.5081869701666666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2665729461761938</v>
+        <v>0.2808400625028807</v>
       </c>
       <c r="T86">
-        <v>4.303275645442642</v>
+        <v>4.581368298019425</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.096376749087787</v>
+        <v>2.071713493216166</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8882,22 +8882,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09592505937543211</v>
+        <v>0.09603232736267323</v>
       </c>
       <c r="C87">
-        <v>0.4704182480307106</v>
+        <v>0.4227545327460676</v>
       </c>
       <c r="D87">
-        <v>2.200918248030712</v>
+        <v>2.198554532746069</v>
       </c>
       <c r="E87">
-        <v>0.6505000000000001</v>
+        <v>0.6958000000000002</v>
       </c>
       <c r="F87">
-        <v>3.850500000000001</v>
+        <v>3.895800000000001</v>
       </c>
       <c r="G87">
         <v>2.12</v>
@@ -8918,28 +8918,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M87">
-        <v>0.2918679000000001</v>
+        <v>0.2953016400000001</v>
       </c>
       <c r="N87">
-        <v>0.3127987666666666</v>
+        <v>0.3093650266666666</v>
       </c>
       <c r="O87">
-        <v>0.05161179649999999</v>
+        <v>0.05104522939999999</v>
       </c>
       <c r="P87">
-        <v>0.2611869701666666</v>
+        <v>0.2583197972666666</v>
       </c>
       <c r="Q87">
-        <v>0.5081869701666666</v>
+        <v>0.5053197972666665</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2808400625028807</v>
+        <v>0.2971453383048087</v>
       </c>
       <c r="T87">
-        <v>4.581368298019425</v>
+        <v>4.899188472392891</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8956,7 +8956,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.071713493216166</v>
+        <v>2.047623801434582</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8964,22 +8964,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09603232736267323</v>
+        <v>0.09613959534991431</v>
       </c>
       <c r="C88">
-        <v>0.4227545327460676</v>
+        <v>0.3750958891227376</v>
       </c>
       <c r="D88">
-        <v>2.198554532746069</v>
+        <v>2.196195889122739</v>
       </c>
       <c r="E88">
-        <v>0.6958000000000002</v>
+        <v>0.7411000000000003</v>
       </c>
       <c r="F88">
-        <v>3.895800000000001</v>
+        <v>3.941100000000001</v>
       </c>
       <c r="G88">
         <v>2.12</v>
@@ -9000,28 +9000,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M88">
-        <v>0.2953016400000001</v>
+        <v>0.2987353800000001</v>
       </c>
       <c r="N88">
-        <v>0.3093650266666666</v>
+        <v>0.3059312866666666</v>
       </c>
       <c r="O88">
-        <v>0.05104522939999999</v>
+        <v>0.05047866229999999</v>
       </c>
       <c r="P88">
-        <v>0.2583197972666666</v>
+        <v>0.2554526243666666</v>
       </c>
       <c r="Q88">
-        <v>0.5053197972666665</v>
+        <v>0.5024526243666666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2971453383048087</v>
+        <v>0.315959118076264</v>
       </c>
       <c r="T88">
-        <v>4.899188472392891</v>
+        <v>5.265904058208428</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -9038,7 +9038,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.047623801434582</v>
+        <v>2.024087895670966</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9046,22 +9046,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09613959534991431</v>
+        <v>0.09624686333715543</v>
       </c>
       <c r="C89">
-        <v>0.3750958891227376</v>
+        <v>0.3274423008553407</v>
       </c>
       <c r="D89">
-        <v>2.196195889122739</v>
+        <v>2.193842300855342</v>
       </c>
       <c r="E89">
-        <v>0.7411000000000003</v>
+        <v>0.7864000000000004</v>
       </c>
       <c r="F89">
-        <v>3.941100000000001</v>
+        <v>3.986400000000001</v>
       </c>
       <c r="G89">
         <v>2.12</v>
@@ -9082,28 +9082,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M89">
-        <v>0.2987353800000001</v>
+        <v>0.3021691200000001</v>
       </c>
       <c r="N89">
-        <v>0.3059312866666666</v>
+        <v>0.3024975466666666</v>
       </c>
       <c r="O89">
-        <v>0.05047866229999999</v>
+        <v>0.04991209519999999</v>
       </c>
       <c r="P89">
-        <v>0.2554526243666666</v>
+        <v>0.2525854514666666</v>
       </c>
       <c r="Q89">
-        <v>0.5024526243666666</v>
+        <v>0.4995854514666666</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.315959118076264</v>
+        <v>0.3379085278096285</v>
       </c>
       <c r="T89">
-        <v>5.265904058208428</v>
+        <v>5.693738908326556</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.024087895670966</v>
+        <v>2.001086896856523</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9128,22 +9128,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09624686333715543</v>
+        <v>0.1069068613243965</v>
       </c>
       <c r="C90">
-        <v>0.3274423008553407</v>
+        <v>0.07098762494420807</v>
       </c>
       <c r="D90">
-        <v>2.193842300855342</v>
+        <v>1.982687624944208</v>
       </c>
       <c r="E90">
-        <v>0.7864000000000004</v>
+        <v>0.8317000000000001</v>
       </c>
       <c r="F90">
-        <v>3.986400000000001</v>
+        <v>4.031700000000001</v>
       </c>
       <c r="G90">
         <v>2.12</v>
@@ -9164,45 +9164,45 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M90">
-        <v>0.3021691200000001</v>
+        <v>0.362853</v>
       </c>
       <c r="N90">
-        <v>0.3024975466666666</v>
+        <v>0.2418136666666666</v>
       </c>
       <c r="O90">
-        <v>0.04991209519999999</v>
+        <v>0.039899255</v>
       </c>
       <c r="P90">
-        <v>0.2525854514666666</v>
+        <v>0.2019144116666667</v>
       </c>
       <c r="Q90">
-        <v>0.4995854514666666</v>
+        <v>0.4489144116666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3379085278096285</v>
+        <v>0.3638487393126957</v>
       </c>
       <c r="T90">
-        <v>5.693738908326556</v>
+        <v>6.199361913011614</v>
       </c>
       <c r="U90">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V90">
         <v>0.165</v>
       </c>
       <c r="W90">
-        <v>0.063293</v>
+        <v>0.07514999999999999</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.001086896856523</v>
+        <v>1.666423225567011</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9210,22 +9210,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1069068613243965</v>
+        <v>0.1071326993116376</v>
       </c>
       <c r="C91">
-        <v>0.07098762494420807</v>
+        <v>0.02165298481890598</v>
       </c>
       <c r="D91">
-        <v>1.982687624944208</v>
+        <v>1.978652984818907</v>
       </c>
       <c r="E91">
-        <v>0.8317000000000001</v>
+        <v>0.8770000000000002</v>
       </c>
       <c r="F91">
-        <v>4.031700000000001</v>
+        <v>4.077000000000001</v>
       </c>
       <c r="G91">
         <v>2.12</v>
@@ -9246,28 +9246,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M91">
-        <v>0.362853</v>
+        <v>0.3669300000000001</v>
       </c>
       <c r="N91">
-        <v>0.2418136666666666</v>
+        <v>0.2377366666666666</v>
       </c>
       <c r="O91">
-        <v>0.039899255</v>
+        <v>0.03922654999999999</v>
       </c>
       <c r="P91">
-        <v>0.2019144116666667</v>
+        <v>0.1985101166666666</v>
       </c>
       <c r="Q91">
-        <v>0.4489144116666667</v>
+        <v>0.4455101166666666</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3638487393126957</v>
+        <v>0.3949769931163762</v>
       </c>
       <c r="T91">
-        <v>6.199361913011614</v>
+        <v>6.806109518633686</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.666423225567011</v>
+        <v>1.647907411949599</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9292,22 +9292,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1071326993116376</v>
+        <v>0.1073585372988787</v>
       </c>
       <c r="C92">
-        <v>0.02165298481890598</v>
+        <v>-0.02766526819358539</v>
       </c>
       <c r="D92">
-        <v>1.978652984818907</v>
+        <v>1.974634731806415</v>
       </c>
       <c r="E92">
-        <v>0.8770000000000002</v>
+        <v>0.9223000000000003</v>
       </c>
       <c r="F92">
-        <v>4.077000000000001</v>
+        <v>4.122300000000001</v>
       </c>
       <c r="G92">
         <v>2.12</v>
@@ -9328,28 +9328,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M92">
-        <v>0.3669300000000001</v>
+        <v>0.3710070000000001</v>
       </c>
       <c r="N92">
-        <v>0.2377366666666666</v>
+        <v>0.2336596666666666</v>
       </c>
       <c r="O92">
-        <v>0.03922654999999999</v>
+        <v>0.03855384499999999</v>
       </c>
       <c r="P92">
-        <v>0.1985101166666666</v>
+        <v>0.1951058216666666</v>
       </c>
       <c r="Q92">
-        <v>0.4455101166666666</v>
+        <v>0.4421058216666666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3949769931163762</v>
+        <v>0.4330226366542081</v>
       </c>
       <c r="T92">
-        <v>6.806109518633686</v>
+        <v>7.547689925505106</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.647907411949599</v>
+        <v>1.629798539290813</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9374,22 +9374,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1073585372988787</v>
+        <v>0.1075843752861198</v>
       </c>
       <c r="C93">
-        <v>-0.02766526819358539</v>
+        <v>-0.07696723372788572</v>
       </c>
       <c r="D93">
-        <v>1.974634731806415</v>
+        <v>1.970632766272115</v>
       </c>
       <c r="E93">
-        <v>0.9223000000000003</v>
+        <v>0.9676000000000005</v>
       </c>
       <c r="F93">
-        <v>4.122300000000001</v>
+        <v>4.167600000000001</v>
       </c>
       <c r="G93">
         <v>2.12</v>
@@ -9410,28 +9410,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M93">
-        <v>0.3710070000000001</v>
+        <v>0.3750840000000001</v>
       </c>
       <c r="N93">
-        <v>0.2336596666666666</v>
+        <v>0.2295826666666666</v>
       </c>
       <c r="O93">
-        <v>0.03855384499999999</v>
+        <v>0.03788113999999999</v>
       </c>
       <c r="P93">
-        <v>0.1951058216666666</v>
+        <v>0.1917015266666666</v>
       </c>
       <c r="Q93">
-        <v>0.4421058216666666</v>
+        <v>0.4387015266666666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4330226366542081</v>
+        <v>0.4805796910764981</v>
       </c>
       <c r="T93">
-        <v>7.547689925505106</v>
+        <v>8.474665434094385</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.629798539290813</v>
+        <v>1.612083337776782</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9456,22 +9456,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1075843752861198</v>
+        <v>0.1078102132733609</v>
       </c>
       <c r="C94">
-        <v>-0.07696723372788572</v>
+        <v>-0.1262530106125377</v>
       </c>
       <c r="D94">
-        <v>1.970632766272115</v>
+        <v>1.966646989387463</v>
       </c>
       <c r="E94">
-        <v>0.9676000000000005</v>
+        <v>1.012900000000001</v>
       </c>
       <c r="F94">
-        <v>4.167600000000001</v>
+        <v>4.212900000000001</v>
       </c>
       <c r="G94">
         <v>2.12</v>
@@ -9492,28 +9492,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M94">
-        <v>0.3750840000000001</v>
+        <v>0.3791610000000001</v>
       </c>
       <c r="N94">
-        <v>0.2295826666666666</v>
+        <v>0.2255056666666666</v>
       </c>
       <c r="O94">
-        <v>0.03788113999999999</v>
+        <v>0.03720843499999999</v>
       </c>
       <c r="P94">
-        <v>0.1917015266666666</v>
+        <v>0.1882972316666666</v>
       </c>
       <c r="Q94">
-        <v>0.4387015266666666</v>
+        <v>0.4352972316666666</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4805796910764981</v>
+        <v>0.5417244753337278</v>
       </c>
       <c r="T94">
-        <v>8.474665434094385</v>
+        <v>9.666491087994883</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9530,7 +9530,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.612083337776782</v>
+        <v>1.594749108338322</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9538,22 +9538,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1078102132733609</v>
+        <v>0.108036051260602</v>
       </c>
       <c r="C95">
-        <v>-0.1262530106125377</v>
+        <v>-0.1755226968781392</v>
       </c>
       <c r="D95">
-        <v>1.966646989387463</v>
+        <v>1.962677303121862</v>
       </c>
       <c r="E95">
-        <v>1.012900000000001</v>
+        <v>1.058200000000001</v>
       </c>
       <c r="F95">
-        <v>4.212900000000001</v>
+        <v>4.258200000000001</v>
       </c>
       <c r="G95">
         <v>2.12</v>
@@ -9574,28 +9574,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M95">
-        <v>0.3791610000000001</v>
+        <v>0.3832380000000001</v>
       </c>
       <c r="N95">
-        <v>0.2255056666666666</v>
+        <v>0.2214286666666666</v>
       </c>
       <c r="O95">
-        <v>0.03720843499999999</v>
+        <v>0.03653572999999999</v>
       </c>
       <c r="P95">
-        <v>0.1882972316666666</v>
+        <v>0.1848929366666666</v>
       </c>
       <c r="Q95">
-        <v>0.4352972316666666</v>
+        <v>0.4318929366666666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5417244753337278</v>
+        <v>0.6232508543433676</v>
       </c>
       <c r="T95">
-        <v>9.666491087994883</v>
+        <v>11.25559195986222</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.594749108338322</v>
+        <v>1.57778369229217</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9620,22 +9620,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.108036051260602</v>
+        <v>0.1082618892478431</v>
       </c>
       <c r="C96">
-        <v>-0.1755226968781392</v>
+        <v>-0.2247763897653812</v>
       </c>
       <c r="D96">
-        <v>1.962677303121862</v>
+        <v>1.95872361023462</v>
       </c>
       <c r="E96">
-        <v>1.058200000000001</v>
+        <v>1.103500000000001</v>
       </c>
       <c r="F96">
-        <v>4.258200000000001</v>
+        <v>4.303500000000001</v>
       </c>
       <c r="G96">
         <v>2.12</v>
@@ -9656,28 +9656,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M96">
-        <v>0.3832380000000001</v>
+        <v>0.3873150000000001</v>
       </c>
       <c r="N96">
-        <v>0.2214286666666666</v>
+        <v>0.2173516666666666</v>
       </c>
       <c r="O96">
-        <v>0.03653572999999999</v>
+        <v>0.03586302499999999</v>
       </c>
       <c r="P96">
-        <v>0.1848929366666666</v>
+        <v>0.1814886416666666</v>
       </c>
       <c r="Q96">
-        <v>0.4318929366666666</v>
+        <v>0.4284886416666666</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6232508543433676</v>
+        <v>0.7373877849568635</v>
       </c>
       <c r="T96">
-        <v>11.25559195986222</v>
+        <v>13.48033318047648</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.57778369229217</v>
+        <v>1.561175442899621</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9702,22 +9702,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1082618892478431</v>
+        <v>0.1084877272350842</v>
       </c>
       <c r="C97">
-        <v>-0.2247763897653812</v>
+        <v>-0.2740141857329892</v>
       </c>
       <c r="D97">
-        <v>1.95872361023462</v>
+        <v>1.954785814267012</v>
       </c>
       <c r="E97">
-        <v>1.103500000000001</v>
+        <v>1.148800000000001</v>
       </c>
       <c r="F97">
-        <v>4.303500000000001</v>
+        <v>4.348800000000002</v>
       </c>
       <c r="G97">
         <v>2.12</v>
@@ -9738,28 +9738,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M97">
-        <v>0.3873150000000001</v>
+        <v>0.3913920000000001</v>
       </c>
       <c r="N97">
-        <v>0.2173516666666666</v>
+        <v>0.2132746666666666</v>
       </c>
       <c r="O97">
-        <v>0.03586302499999999</v>
+        <v>0.03519031999999998</v>
       </c>
       <c r="P97">
-        <v>0.1814886416666666</v>
+        <v>0.1780843466666666</v>
       </c>
       <c r="Q97">
-        <v>0.4284886416666666</v>
+        <v>0.4250843466666666</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7373877849568635</v>
+        <v>0.9085931808771074</v>
       </c>
       <c r="T97">
-        <v>13.48033318047648</v>
+        <v>16.81744501139789</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.561175442899621</v>
+        <v>1.544913198702749</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9784,22 +9784,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1084877272350842</v>
+        <v>0.1087135652223253</v>
       </c>
       <c r="C98">
-        <v>-0.2740141857329883</v>
+        <v>-0.3232361804655657</v>
       </c>
       <c r="D98">
-        <v>1.954785814267012</v>
+        <v>1.950863819534435</v>
       </c>
       <c r="E98">
-        <v>1.1488</v>
+        <v>1.1941</v>
       </c>
       <c r="F98">
-        <v>4.348800000000001</v>
+        <v>4.394100000000001</v>
       </c>
       <c r="G98">
         <v>2.12</v>
@@ -9820,28 +9820,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M98">
-        <v>0.391392</v>
+        <v>0.3954690000000001</v>
       </c>
       <c r="N98">
-        <v>0.2132746666666667</v>
+        <v>0.2091976666666666</v>
       </c>
       <c r="O98">
-        <v>0.03519032</v>
+        <v>0.03451761499999999</v>
       </c>
       <c r="P98">
-        <v>0.1780843466666667</v>
+        <v>0.1746800516666666</v>
       </c>
       <c r="Q98">
-        <v>0.4250843466666667</v>
+        <v>0.4216800516666666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9085931808771049</v>
+        <v>1.193935507410844</v>
       </c>
       <c r="T98">
-        <v>16.81744501139784</v>
+        <v>22.37929806293349</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.54491319870275</v>
+        <v>1.528986258509938</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9866,22 +9866,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1087135652223253</v>
+        <v>0.1089394032095664</v>
       </c>
       <c r="C99">
-        <v>-0.3232361804655657</v>
+        <v>-0.3724424688813439</v>
       </c>
       <c r="D99">
-        <v>1.950863819534435</v>
+        <v>1.946957531118656</v>
       </c>
       <c r="E99">
-        <v>1.1941</v>
+        <v>1.2394</v>
       </c>
       <c r="F99">
-        <v>4.394100000000001</v>
+        <v>4.439400000000001</v>
       </c>
       <c r="G99">
         <v>2.12</v>
@@ -9902,28 +9902,28 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M99">
-        <v>0.3954690000000001</v>
+        <v>0.3995460000000001</v>
       </c>
       <c r="N99">
-        <v>0.2091976666666666</v>
+        <v>0.2051206666666666</v>
       </c>
       <c r="O99">
-        <v>0.03451761499999999</v>
+        <v>0.03384490999999999</v>
       </c>
       <c r="P99">
-        <v>0.1746800516666666</v>
+        <v>0.1712757566666666</v>
       </c>
       <c r="Q99">
-        <v>0.4216800516666666</v>
+        <v>0.4182757566666666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.193935507410844</v>
+        <v>1.76462016047832</v>
       </c>
       <c r="T99">
-        <v>22.37929806293349</v>
+        <v>33.50300416600478</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.528986258509938</v>
+        <v>1.513384357912898</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9948,22 +9948,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1089394032095664</v>
+        <v>0.1586207095348192</v>
       </c>
       <c r="C100">
-        <v>-0.3724424688813439</v>
+        <v>-1.013103516246931</v>
       </c>
       <c r="D100">
-        <v>1.946957531118656</v>
+        <v>1.35159648375307</v>
       </c>
       <c r="E100">
-        <v>1.2394</v>
+        <v>1.2847</v>
       </c>
       <c r="F100">
-        <v>4.439400000000001</v>
+        <v>4.484700000000001</v>
       </c>
       <c r="G100">
         <v>2.12</v>
@@ -9984,129 +9984,47 @@
         <v>0.6046666666666667</v>
       </c>
       <c r="M100">
-        <v>0.3995460000000001</v>
+        <v>0.6583539600000002</v>
       </c>
       <c r="N100">
-        <v>0.2051206666666666</v>
+        <v>-0.05368729333333355</v>
       </c>
       <c r="O100">
-        <v>0.03384490999999999</v>
+        <v>-0.008858403400000037</v>
       </c>
       <c r="P100">
-        <v>0.1712757566666666</v>
+        <v>-0.04482888993333352</v>
       </c>
       <c r="Q100">
-        <v>0.4182757566666666</v>
+        <v>0.2021711100666665</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.76462016047832</v>
+        <v>3.531299209552551</v>
       </c>
       <c r="T100">
-        <v>33.50300416600478</v>
+        <v>67.93886715044636</v>
       </c>
       <c r="U100">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.165</v>
+        <v>0.1515446189463187</v>
       </c>
       <c r="W100">
-        <v>0.07514999999999999</v>
+        <v>0.1245532499386804</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.513384357912898</v>
+        <v>0.9184522360382954</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1586207095348192</v>
-      </c>
-      <c r="C101">
-        <v>-1.013103516246931</v>
-      </c>
-      <c r="D101">
-        <v>1.35159648375307</v>
-      </c>
-      <c r="E101">
-        <v>1.2847</v>
-      </c>
-      <c r="F101">
-        <v>4.484700000000001</v>
-      </c>
-      <c r="G101">
-        <v>2.12</v>
-      </c>
-      <c r="H101">
-        <v>1.33</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.8516666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.247</v>
-      </c>
-      <c r="L101">
-        <v>0.6046666666666667</v>
-      </c>
-      <c r="M101">
-        <v>0.6583539600000002</v>
-      </c>
-      <c r="N101">
-        <v>-0.05368729333333355</v>
-      </c>
-      <c r="O101">
-        <v>-0.008858403400000037</v>
-      </c>
-      <c r="P101">
-        <v>-0.04482888993333352</v>
-      </c>
-      <c r="Q101">
-        <v>0.2021711100666665</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.531299209552551</v>
-      </c>
-      <c r="T101">
-        <v>67.93886715044636</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1515446189463187</v>
-      </c>
-      <c r="W101">
-        <v>0.1245532499386804</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9184522360382954</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
